--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3986B0-6238-44DF-8D8C-9EBBFA5F22C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFE19EE-9B29-45BF-B28A-7BC621748FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1605" windowWidth="34725" windowHeight="18735" firstSheet="3" activeTab="6" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="13" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -25,25 +25,27 @@
     <sheet name="champion_header" sheetId="9" r:id="rId10"/>
     <sheet name="champion_spell_header" sheetId="13" r:id="rId11"/>
     <sheet name="item_header" sheetId="10" r:id="rId12"/>
-    <sheet name="anvil_header" sheetId="11" r:id="rId13"/>
-    <sheet name="TFTSet_header" sheetId="15" r:id="rId14"/>
-    <sheet name="TFTShop_header" sheetId="17" r:id="rId15"/>
-    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId16"/>
-    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId17"/>
-    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId18"/>
-    <sheet name="TFTRound_header" sheetId="19" r:id="rId19"/>
-    <sheet name="TFTPortal_header" sheetId="27" r:id="rId20"/>
-    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId21"/>
-    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId22"/>
-    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId23"/>
-    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId24"/>
-    <sheet name="TFTItemList_header" sheetId="22" r:id="rId25"/>
-    <sheet name="TFTItem_header" sheetId="23" r:id="rId26"/>
-    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId27"/>
-    <sheet name="TFTTrait_header" sheetId="25" r:id="rId28"/>
-    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId29"/>
-    <sheet name="TFTScript_header" sheetId="26" r:id="rId30"/>
-    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId31"/>
+    <sheet name="itemGroup_header" sheetId="38" r:id="rId13"/>
+    <sheet name="itemModifier_header" sheetId="39" r:id="rId14"/>
+    <sheet name="anvil_header" sheetId="11" r:id="rId15"/>
+    <sheet name="TFTSet_header" sheetId="15" r:id="rId16"/>
+    <sheet name="TFTShop_header" sheetId="17" r:id="rId17"/>
+    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId18"/>
+    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId19"/>
+    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId20"/>
+    <sheet name="TFTRound_header" sheetId="19" r:id="rId21"/>
+    <sheet name="TFTPortal_header" sheetId="27" r:id="rId22"/>
+    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId23"/>
+    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId24"/>
+    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId25"/>
+    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId26"/>
+    <sheet name="TFTItemList_header" sheetId="22" r:id="rId27"/>
+    <sheet name="TFTItem_header" sheetId="23" r:id="rId28"/>
+    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId29"/>
+    <sheet name="TFTTrait_header" sheetId="25" r:id="rId30"/>
+    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId31"/>
+    <sheet name="TFTScript_header" sheetId="26" r:id="rId32"/>
+    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">champion_spell_header!$A$1:$G$341</definedName>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6598" uniqueCount="3386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6817" uniqueCount="3497">
   <si>
     <t>key</t>
   </si>
@@ -12112,6 +12114,411 @@
   </si>
   <si>
     <t>mDynamicTooltipText_content_en</t>
+  </si>
+  <si>
+    <t>mItemGroupID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mItemModifiers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mInventorySlotMin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mMaxGroupOwnable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{dbc029fa}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mPurchaseCooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mInventorySlotMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备分组名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备修饰方案</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备栏最大槽位号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备栏最小槽位号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>组内最多持有装备数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连点预防间隔（秒）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mItemModifierID</t>
+  </si>
+  <si>
+    <t>mModifiedIfBuildsFromItem</t>
+  </si>
+  <si>
+    <t>mModifiedItem</t>
+  </si>
+  <si>
+    <t>mDeltaMaxStacks</t>
+  </si>
+  <si>
+    <t>mModifiedGroup</t>
+  </si>
+  <si>
+    <t>mMaximumModifierInstancesToBeActive</t>
+  </si>
+  <si>
+    <t>{06d9d838}</t>
+  </si>
+  <si>
+    <t>{917537a9}</t>
+  </si>
+  <si>
+    <t>mModifierIsInheritedByOwnedParentItems</t>
+  </si>
+  <si>
+    <t>mIgnoreSpecificMaxGroupOwnable</t>
+  </si>
+  <si>
+    <t>mMaximumDeltasToStack</t>
+  </si>
+  <si>
+    <t>mShowAsModifiedInUI</t>
+  </si>
+  <si>
+    <t>mDeltaGoldCostPercent</t>
+  </si>
+  <si>
+    <t>mDeltaRequiredLevel</t>
+  </si>
+  <si>
+    <t>mDeltaGoldCost</t>
+  </si>
+  <si>
+    <t>mDescriptionToReplace</t>
+  </si>
+  <si>
+    <t>mDynamicTooltipToReplace</t>
+  </si>
+  <si>
+    <t>mVisualPriority</t>
+  </si>
+  <si>
+    <t>inventoryIconToOverlay</t>
+  </si>
+  <si>
+    <t>mDescriptionToAppend</t>
+  </si>
+  <si>
+    <t>mDynamicTooltipToAppend</t>
+  </si>
+  <si>
+    <t>mDisplayNameToAppend</t>
+  </si>
+  <si>
+    <t>mDisplayNameToReplace</t>
+  </si>
+  <si>
+    <t>mDisplayNameToPrepend</t>
+  </si>
+  <si>
+    <t>mClickableToEnable</t>
+  </si>
+  <si>
+    <t>mSpellNameToReplace</t>
+  </si>
+  <si>
+    <t>{20b65c83}</t>
+  </si>
+  <si>
+    <t>装备修饰名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰构件装备名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰构件装备名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰装备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mModifiedItem_mDisplayName_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mModifiedIfBuildsFromItem_mDisplayName_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mModifiedItem_mDisplayName_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰装备名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰装备名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大持有数量变化值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大生效实例数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰装备分组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{06d9d838}_mDisplayName_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{06d9d838}_mDisplayName_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{917537a9}_mDisplayName_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{917537a9}_mDisplayName_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰前的基础构件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰后的基础构件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰前的基础构件名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰前的基础构件名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰后的基础构件名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰后的基础构件名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大件继承构件修饰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不受其它最大持有数量限制影响</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示为已修饰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所需等级变化值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDescriptionToReplace_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDescriptionToReplace_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代简述键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代简述（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代简述（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代动态详细信息键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDynamicTooltipToReplace_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDynamicTooltipToReplace_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代动态详细信息（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代动态详细信息（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备栏覆盖图标路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加简述键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加动态详细信息键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDescriptionToAppend_content_zh</t>
+  </si>
+  <si>
+    <t>mDescriptionToAppend_content_en</t>
+  </si>
+  <si>
+    <t>mDynamicTooltipToAppend_content_zh</t>
+  </si>
+  <si>
+    <t>mDynamicTooltipToAppend_content_en</t>
+  </si>
+  <si>
+    <t>追加简述（中文）</t>
+  </si>
+  <si>
+    <t>追加简述（英文）</t>
+  </si>
+  <si>
+    <t>追加动态详细信息（中文）</t>
+  </si>
+  <si>
+    <t>追加动态详细信息（英文）</t>
+  </si>
+  <si>
+    <t>追加显示名键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代显示名键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前附显示名键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDisplayNameToAppend_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加显示名（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDisplayNameToAppend_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加显示名（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>替代显示名（中文）</t>
+  </si>
+  <si>
+    <t>替代显示名（英文）</t>
+  </si>
+  <si>
+    <t>mDisplayNameToReplace_content_zh</t>
+  </si>
+  <si>
+    <t>mDisplayNameToReplace_content_en</t>
+  </si>
+  <si>
+    <t>mDisplayNameToPrepend_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mDisplayNameToPrepend_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前附显示名（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前附显示名（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单击使用技能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取代技能名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级边框方案名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成构件包含以下装备时修饰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mModifiedIfBuildsFromItem_mDisplayName_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定价格变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果叠加次数最大变化量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>计分板排列优先级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -35318,6 +35725,1284 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60A5A8D-F208-4F04-9C5D-CD73D509CE53}">
+  <sheetPr codeName="Sheet22"/>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3386</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3393</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3392</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3395</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3389</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3397</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3390</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3391</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3398</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G9">
+    <sortCondition ref="A1:A9"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B064C7-3D64-42BC-A4D2-303DDDFAC1AC}">
+  <sheetPr codeName="Sheet23"/>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="56" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3399</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3426</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3400</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3492</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3429</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3402</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3435</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3403</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3437</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3404</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3436</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3405</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3442</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3443</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3448</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3408</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3449</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3495</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3410</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3450</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3411</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3451</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>3412</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3452</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3413</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3494</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>3414</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3455</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3415</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3458</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3496</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>3417</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3463</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>3418</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3464</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>3419</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3465</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>3420</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3474</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>3421</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3475</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3422</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3476</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>3423</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3489</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>3424</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3490</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>3425</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3491</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>3493</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3428</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>3431</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3427</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>3430</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3433</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3434</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>3438</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3444</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3439</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3445</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3446</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3441</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3447</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3456</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3454</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3457</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3459</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3461</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3460</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3462</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3466</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3470</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3471</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3468</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3472</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3469</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3473</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3478</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3480</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>3483</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3481</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C49" t="s">
+        <v>3482</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3487</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3488</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
+    <sortCondition ref="A1:A51"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457E3F81-9310-44BF-90A4-FF51EB2CBED2}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G28"/>
@@ -35832,7 +37517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3901968F-E5DF-4CBD-ADFB-08FA8A3F4044}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G299"/>
@@ -40115,7 +41800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40963FC-D1AF-47E5-BB09-9770285565C2}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G27"/>
@@ -40615,8 +42300,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEED51C0-16CE-493B-ACDF-CED633B09365}">
+  <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -40777,7 +42463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6ED802-F57E-44A6-B120-12D8C7BE7DFE}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G9"/>
@@ -40915,1526 +42601,6 @@
       <c r="E9" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="39.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2957</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2956</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2967</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2958</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>2974</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2973</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>2968</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2575</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>2969</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2971</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>2970</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2972</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
-  <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2575</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="G4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2576</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2566</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2577</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2567</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2578</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2568</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2579</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="G8">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2569</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2580</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="G9">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2570</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2581</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="G10">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>2571</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2582</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2572</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2583</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>2573</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2584</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2585</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2595</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>2586</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2596</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>2587</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2597</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2588</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2598</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2592</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2589</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2593</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2590</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>2594</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2591</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>2599</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2601</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2600</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2602</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>2603</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2609</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>2604</v>
-      </c>
-      <c r="C24" t="s">
-        <v>2610</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>2605</v>
-      </c>
-      <c r="C25" t="s">
-        <v>2611</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>2606</v>
-      </c>
-      <c r="C26" t="s">
-        <v>2612</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>2607</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2613</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>2608</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2640</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>2614</v>
-      </c>
-      <c r="C29" t="s">
-        <v>2618</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>2615</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2619</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>2616</v>
-      </c>
-      <c r="C31" t="s">
-        <v>2620</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>2617</v>
-      </c>
-      <c r="C32" t="s">
-        <v>2621</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>2630</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2635</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>2631</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2636</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>2632</v>
-      </c>
-      <c r="C35" t="s">
-        <v>2637</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>2633</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2638</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>2634</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2639</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>2641</v>
-      </c>
-      <c r="C38" t="s">
-        <v>2645</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>2642</v>
-      </c>
-      <c r="C39" t="s">
-        <v>2646</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>2643</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2647</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>2644</v>
-      </c>
-      <c r="C41" t="s">
-        <v>2648</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>2649</v>
-      </c>
-      <c r="C42" t="s">
-        <v>2651</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>2650</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2652</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>2653</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2657</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>2654</v>
-      </c>
-      <c r="C45" t="s">
-        <v>2658</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>2655</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2659</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>2656</v>
-      </c>
-      <c r="C47" t="s">
-        <v>2660</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>2574</v>
-      </c>
-      <c r="C48" t="s">
-        <v>2173</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="G48">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2661</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2552</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2663</v>
-      </c>
-      <c r="C51" t="s">
-        <v>2664</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2665</v>
-      </c>
-      <c r="C52" t="s">
-        <v>2666</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C53" t="s">
-        <v>2669</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2668</v>
-      </c>
-      <c r="C54" t="s">
-        <v>2670</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2671</v>
-      </c>
-      <c r="C55" t="s">
-        <v>2673</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2672</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2674</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2675</v>
-      </c>
-      <c r="C57" t="s">
-        <v>2676</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2677</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2678</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2679</v>
-      </c>
-      <c r="C59" t="s">
-        <v>2680</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2681</v>
-      </c>
-      <c r="C60" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G60">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2683</v>
-      </c>
-      <c r="C61" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2684</v>
-      </c>
-      <c r="C62" t="s">
-        <v>2686</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2695</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>62</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>2696</v>
-      </c>
-      <c r="C64" t="s">
-        <v>2698</v>
-      </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G64">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>2687</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2689</v>
-      </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>2688</v>
-      </c>
-      <c r="C66" t="s">
-        <v>2690</v>
-      </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C67" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G67">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>2693</v>
-      </c>
-      <c r="C68" t="s">
-        <v>2694</v>
-      </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G68">
-    <sortCondition ref="A1:A68"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42639,7 +42805,1529 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
+  <sheetPr codeName="Sheet25"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="39.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2973</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2575</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>2969</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="6"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2579</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="G8">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="G9">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="G10">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2571</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>2594</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2621</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2630</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2633</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2641</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2645</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2646</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2644</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2649</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2655</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="G48">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G68">
+    <sortCondition ref="A1:A68"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B1F2EF-0DC6-4BB2-8172-4E4198527108}">
+  <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -43128,8 +44816,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
+  <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -43315,8 +45004,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
+  <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -43639,7 +45329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G10"/>
@@ -43860,7 +45550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78003282-BF12-4B9E-88E0-0647BA982AE8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G29"/>
@@ -44338,7 +46028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8BF486-9605-4C14-9D33-B85EFC67F833}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G11"/>
@@ -44520,8 +46210,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF0C918-C1C4-4CA0-AE17-312A0FD1DCCE}">
+  <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -45476,8 +47167,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC122C9-2D95-4069-BA3C-DDFB1C7F608D}">
+  <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -45634,641 +47326,6 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G7">
     <sortCondition ref="A1:A7"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="58.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2839</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2840</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2766</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2841</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2847</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2842</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2834</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2843</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2835</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2844</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2836</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2860</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>2837</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2861</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2838</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>2551</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2845</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>2552</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2846</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>2824</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2852</v>
-      </c>
-      <c r="G15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>2825</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2853</v>
-      </c>
-      <c r="G16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>2826</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2854</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>2827</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2855</v>
-      </c>
-      <c r="G18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>2848</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2856</v>
-      </c>
-      <c r="G19">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>2849</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2857</v>
-      </c>
-      <c r="G20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>2850</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2858</v>
-      </c>
-      <c r="G21">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>2851</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2859</v>
-      </c>
-      <c r="G22">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G22">
-    <sortCondition ref="A1:A22"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="54.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2699</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2775</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2979</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2997</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2980</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2988</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2981</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2989</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2982</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2990</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2983</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2991</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2709</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2992</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2984</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2993</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>2985</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2994</v>
-      </c>
-      <c r="G11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>2986</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2995</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>2987</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2996</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G13">
-    <sortCondition ref="A1:A13"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47192,7 +48249,645 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
+  <sheetPr codeName="Sheet31"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="58.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2840</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2834</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2843</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2845</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2846</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2852</v>
+      </c>
+      <c r="G15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2853</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2854</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2855</v>
+      </c>
+      <c r="G18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2856</v>
+      </c>
+      <c r="G19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2857</v>
+      </c>
+      <c r="G20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2859</v>
+      </c>
+      <c r="G22">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G22">
+    <sortCondition ref="A1:A22"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
+  <sheetPr codeName="Sheet32"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="54.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2997</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2983</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2991</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2992</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2993</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2994</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2995</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G13">
+    <sortCondition ref="A1:A13"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EAFC06-5BD2-40F9-AAC9-8F399DCA30B2}">
+  <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -47331,7 +49026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:G10"/>
@@ -47536,6 +49231,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7F4C24-7612-49A7-BA2B-B3643B323BBD}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -48844,6 +50540,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7D9E21-BBB5-4A35-B254-A9AA06BCF8B0}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -49544,6 +51241,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEC55FC-26A9-4869-A0C1-950FCC7DF8BC}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -50020,6 +51718,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8B5E4A-9F14-46D9-A3E4-C039ADD42EB8}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -51003,6 +52702,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BF9C7C-6735-47CD-AD6E-C4479D5531D4}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C015DD4D-2E02-4924-BA8F-72C64634F31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB69180-9B45-4B8A-86F9-35B5325578C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="15" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6869" uniqueCount="3527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="3523">
   <si>
     <t>key</t>
   </si>
@@ -12604,14 +12604,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1ff99d7f} {bff2f361}_content_zh_burn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1ff99d7f} {bff2f361}_content_en_burn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{1ff99d7f} {3b7aa707}_content_zh_burn</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -12624,12 +12616,6 @@
   </si>
   <si>
     <t>详细信息（英文/去格式化）</t>
-  </si>
-  <si>
-    <t>简述（中文/去格式化）</t>
-  </si>
-  <si>
-    <t>简述（英文/去格式化）</t>
   </si>
 </sst>
 </file>
@@ -20322,7 +20308,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF611F9-13A5-4CF6-B8E3-E0A2C9AC1592}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
@@ -20440,7 +20426,7 @@
       </c>
       <c r="E6" s="4"/>
       <c r="G6">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20458,7 +20444,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="G7">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20476,7 +20462,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="G8">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20568,13 +20554,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3519</v>
+        <v>3512</v>
       </c>
       <c r="C15" t="s">
-        <v>3525</v>
+        <v>1148</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20582,13 +20568,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3520</v>
+        <v>3513</v>
       </c>
       <c r="C16" t="s">
-        <v>3526</v>
+        <v>1152</v>
       </c>
       <c r="G16">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20596,13 +20582,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>3512</v>
+        <v>3519</v>
       </c>
       <c r="C17" t="s">
-        <v>1148</v>
+        <v>3521</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20610,46 +20596,18 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>3513</v>
+        <v>3520</v>
       </c>
       <c r="C18" t="s">
-        <v>1152</v>
+        <v>3522</v>
       </c>
       <c r="G18">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>3521</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3523</v>
-      </c>
-      <c r="G19">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>3522</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3524</v>
-      </c>
-      <c r="G20">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G20">
-    <sortCondition ref="A1:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
+    <sortCondition ref="A1:A18"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB69180-9B45-4B8A-86F9-35B5325578C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B131E8-8D2B-440F-AFDF-7C82A45ABE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="15" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -11716,66 +11716,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{8662cf12} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4d37af28} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{9eedebad} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{913157bb} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4af40dc3} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{e2b5d80d} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ea6100d5} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{18956a21} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{33c0bf27} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{01262a25} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{e62d9d92} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{7bd4b298} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{836cc82a} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4f89c991} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{b9f2b365} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>基础生命值</t>
   </si>
   <si>
@@ -11821,31 +11761,6 @@
     <t>成长攻击速度</t>
   </si>
   <si>
-    <t>primaryAbilityResource {726ee5cd} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>primaryAbilityResource {6216bf7b} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>primaryAbilityResource {b35aa769} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>primaryAbilityResource {3a509002} {b35aa769}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>secondaryAbilityResource {726ee5cd} {b35aa769}</t>
-  </si>
-  <si>
-    <t>secondaryAbilityResource {6216bf7b} {b35aa769}</t>
-  </si>
-  <si>
-    <t>secondaryAbilityResource {b35aa769} {b35aa769}</t>
-  </si>
-  <si>
     <t>OutputOrder1 (champion; before v16.5)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -12616,6 +12531,72 @@
   </si>
   <si>
     <t>详细信息（英文/去格式化）</t>
+  </si>
+  <si>
+    <t>baseHPModifiable baseValue</t>
+  </si>
+  <si>
+    <t>hpPerLevelModifiable baseValue</t>
+  </si>
+  <si>
+    <t>baseStaticHPRegenModifiable baseValue</t>
+  </si>
+  <si>
+    <t>hpRegenPerLevelModifiable baseValue</t>
+  </si>
+  <si>
+    <t>baseDamageModifiable baseValue</t>
+  </si>
+  <si>
+    <t>damagePerLevelModifiable baseValue</t>
+  </si>
+  <si>
+    <t>baseArmorModifiable baseValue</t>
+  </si>
+  <si>
+    <t>armorPerLevelModifiable baseValue</t>
+  </si>
+  <si>
+    <t>baseMR baseValue</t>
+  </si>
+  <si>
+    <t>{01262a25} baseValue</t>
+  </si>
+  <si>
+    <t>baseMoveSpeedModifiable baseValue</t>
+  </si>
+  <si>
+    <t>attackRangeModifiable baseValue</t>
+  </si>
+  <si>
+    <t>attackSpeedModifiable baseValue</t>
+  </si>
+  <si>
+    <t>attackSpeedRatioModifiable baseValue</t>
+  </si>
+  <si>
+    <t>attackSpeedPerLevelModifiable baseValue</t>
+  </si>
+  <si>
+    <t>primaryAbilityResource {726ee5cd} baseValue</t>
+  </si>
+  <si>
+    <t>primaryAbilityResource {6216bf7b} baseValue</t>
+  </si>
+  <si>
+    <t>primaryAbilityResource baseValue baseValue</t>
+  </si>
+  <si>
+    <t>primaryAbilityResource {3a509002} baseValue</t>
+  </si>
+  <si>
+    <t>secondaryAbilityResource {726ee5cd} baseValue</t>
+  </si>
+  <si>
+    <t>secondaryAbilityResource {6216bf7b} baseValue</t>
+  </si>
+  <si>
+    <t>secondaryAbilityResource baseValue baseValue</t>
   </si>
 </sst>
 </file>
@@ -16917,10 +16898,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3399</v>
+        <v>3377</v>
       </c>
       <c r="C3" t="s">
-        <v>3426</v>
+        <v>3404</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -16934,10 +16915,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3400</v>
+        <v>3378</v>
       </c>
       <c r="C4" t="s">
-        <v>3492</v>
+        <v>3470</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -16954,10 +16935,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3401</v>
+        <v>3379</v>
       </c>
       <c r="C5" t="s">
-        <v>3429</v>
+        <v>3407</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -16974,10 +16955,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3402</v>
+        <v>3380</v>
       </c>
       <c r="C6" t="s">
-        <v>3435</v>
+        <v>3413</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -16994,10 +16975,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3403</v>
+        <v>3381</v>
       </c>
       <c r="C7" t="s">
-        <v>3437</v>
+        <v>3415</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -17014,10 +16995,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3404</v>
+        <v>3382</v>
       </c>
       <c r="C8" t="s">
-        <v>3436</v>
+        <v>3414</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -17034,10 +17015,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3405</v>
+        <v>3383</v>
       </c>
       <c r="C9" t="s">
-        <v>3442</v>
+        <v>3420</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -17054,10 +17035,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3406</v>
+        <v>3384</v>
       </c>
       <c r="C10" t="s">
-        <v>3443</v>
+        <v>3421</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
@@ -17074,10 +17055,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3407</v>
+        <v>3385</v>
       </c>
       <c r="C11" t="s">
-        <v>3448</v>
+        <v>3426</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
@@ -17097,10 +17078,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3408</v>
+        <v>3386</v>
       </c>
       <c r="C12" t="s">
-        <v>3449</v>
+        <v>3427</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
@@ -17120,10 +17101,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3409</v>
+        <v>3387</v>
       </c>
       <c r="C13" t="s">
-        <v>3495</v>
+        <v>3473</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -17140,10 +17121,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3410</v>
+        <v>3388</v>
       </c>
       <c r="C14" t="s">
-        <v>3450</v>
+        <v>3428</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
@@ -17163,10 +17144,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3411</v>
+        <v>3389</v>
       </c>
       <c r="C15" t="s">
-        <v>3451</v>
+        <v>3429</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
@@ -17183,10 +17164,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3412</v>
+        <v>3390</v>
       </c>
       <c r="C16" t="s">
-        <v>3452</v>
+        <v>3430</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
@@ -17203,10 +17184,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3413</v>
+        <v>3391</v>
       </c>
       <c r="C17" t="s">
-        <v>3494</v>
+        <v>3472</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -17223,10 +17204,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3414</v>
+        <v>3392</v>
       </c>
       <c r="C18" t="s">
-        <v>3455</v>
+        <v>3433</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
@@ -17243,10 +17224,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3415</v>
+        <v>3393</v>
       </c>
       <c r="C19" t="s">
-        <v>3458</v>
+        <v>3436</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
@@ -17263,10 +17244,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3416</v>
+        <v>3394</v>
       </c>
       <c r="C20" t="s">
-        <v>3496</v>
+        <v>3474</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>22</v>
@@ -17283,10 +17264,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3417</v>
+        <v>3395</v>
       </c>
       <c r="C21" t="s">
-        <v>3463</v>
+        <v>3441</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>22</v>
@@ -17303,10 +17284,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3418</v>
+        <v>3396</v>
       </c>
       <c r="C22" t="s">
-        <v>3464</v>
+        <v>3442</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>22</v>
@@ -17323,10 +17304,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3419</v>
+        <v>3397</v>
       </c>
       <c r="C23" t="s">
-        <v>3465</v>
+        <v>3443</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>22</v>
@@ -17343,10 +17324,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3420</v>
+        <v>3398</v>
       </c>
       <c r="C24" t="s">
-        <v>3474</v>
+        <v>3452</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>22</v>
@@ -17363,10 +17344,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3421</v>
+        <v>3399</v>
       </c>
       <c r="C25" t="s">
-        <v>3475</v>
+        <v>3453</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>22</v>
@@ -17383,10 +17364,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3422</v>
+        <v>3400</v>
       </c>
       <c r="C26" t="s">
-        <v>3476</v>
+        <v>3454</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>22</v>
@@ -17403,10 +17384,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3423</v>
+        <v>3401</v>
       </c>
       <c r="C27" t="s">
-        <v>3489</v>
+        <v>3467</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>22</v>
@@ -17426,10 +17407,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3424</v>
+        <v>3402</v>
       </c>
       <c r="C28" t="s">
-        <v>3490</v>
+        <v>3468</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>22</v>
@@ -17446,10 +17427,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3425</v>
+        <v>3403</v>
       </c>
       <c r="C29" t="s">
-        <v>3491</v>
+        <v>3469</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>22</v>
@@ -17466,10 +17447,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>3493</v>
+        <v>3471</v>
       </c>
       <c r="C30" t="s">
-        <v>3428</v>
+        <v>3406</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>22</v>
@@ -17483,10 +17464,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>3431</v>
+        <v>3409</v>
       </c>
       <c r="C31" t="s">
-        <v>3427</v>
+        <v>3405</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>22</v>
@@ -17500,10 +17481,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>3430</v>
+        <v>3408</v>
       </c>
       <c r="C32" t="s">
-        <v>3433</v>
+        <v>3411</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>22</v>
@@ -17517,10 +17498,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>3432</v>
+        <v>3410</v>
       </c>
       <c r="C33" t="s">
-        <v>3434</v>
+        <v>3412</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>22</v>
@@ -17534,10 +17515,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>3438</v>
+        <v>3416</v>
       </c>
       <c r="C34" t="s">
-        <v>3444</v>
+        <v>3422</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>22</v>
@@ -17551,10 +17532,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>3439</v>
+        <v>3417</v>
       </c>
       <c r="C35" t="s">
-        <v>3445</v>
+        <v>3423</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>22</v>
@@ -17568,10 +17549,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>3440</v>
+        <v>3418</v>
       </c>
       <c r="C36" t="s">
-        <v>3446</v>
+        <v>3424</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>22</v>
@@ -17585,10 +17566,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>3441</v>
+        <v>3419</v>
       </c>
       <c r="C37" t="s">
-        <v>3447</v>
+        <v>3425</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>22</v>
@@ -17602,10 +17583,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>3453</v>
+        <v>3431</v>
       </c>
       <c r="C38" t="s">
-        <v>3456</v>
+        <v>3434</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>22</v>
@@ -17619,10 +17600,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>3454</v>
+        <v>3432</v>
       </c>
       <c r="C39" t="s">
-        <v>3457</v>
+        <v>3435</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>22</v>
@@ -17636,10 +17617,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>3459</v>
+        <v>3437</v>
       </c>
       <c r="C40" t="s">
-        <v>3461</v>
+        <v>3439</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>22</v>
@@ -17653,10 +17634,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>3460</v>
+        <v>3438</v>
       </c>
       <c r="C41" t="s">
-        <v>3462</v>
+        <v>3440</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>22</v>
@@ -17670,10 +17651,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>3466</v>
+        <v>3444</v>
       </c>
       <c r="C42" t="s">
-        <v>3470</v>
+        <v>3448</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>22</v>
@@ -17687,10 +17668,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>3467</v>
+        <v>3445</v>
       </c>
       <c r="C43" t="s">
-        <v>3471</v>
+        <v>3449</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>22</v>
@@ -17704,10 +17685,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>3468</v>
+        <v>3446</v>
       </c>
       <c r="C44" t="s">
-        <v>3472</v>
+        <v>3450</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>22</v>
@@ -17721,10 +17702,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>3469</v>
+        <v>3447</v>
       </c>
       <c r="C45" t="s">
-        <v>3473</v>
+        <v>3451</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>22</v>
@@ -17738,10 +17719,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>3477</v>
+        <v>3455</v>
       </c>
       <c r="C46" t="s">
-        <v>3478</v>
+        <v>3456</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>22</v>
@@ -17755,10 +17736,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>3479</v>
+        <v>3457</v>
       </c>
       <c r="C47" t="s">
-        <v>3480</v>
+        <v>3458</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>22</v>
@@ -17772,10 +17753,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>3483</v>
+        <v>3461</v>
       </c>
       <c r="C48" t="s">
-        <v>3481</v>
+        <v>3459</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>22</v>
@@ -17789,10 +17770,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>3484</v>
+        <v>3462</v>
       </c>
       <c r="C49" t="s">
-        <v>3482</v>
+        <v>3460</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>22</v>
@@ -17806,10 +17787,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>3485</v>
+        <v>3463</v>
       </c>
       <c r="C50" t="s">
-        <v>3487</v>
+        <v>3465</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>22</v>
@@ -17823,10 +17804,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>3486</v>
+        <v>3464</v>
       </c>
       <c r="C51" t="s">
-        <v>3488</v>
+        <v>3466</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>22</v>
@@ -20362,10 +20343,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3499</v>
+        <v>3477</v>
       </c>
       <c r="C3" t="s">
-        <v>3503</v>
+        <v>3481</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -20380,10 +20361,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3500</v>
+        <v>3478</v>
       </c>
       <c r="C4" t="s">
-        <v>3516</v>
+        <v>3494</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -20398,7 +20379,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3501</v>
+        <v>3479</v>
       </c>
       <c r="C5" t="s">
         <v>2891</v>
@@ -20416,7 +20397,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3502</v>
+        <v>3480</v>
       </c>
       <c r="C6" t="s">
         <v>1082</v>
@@ -20434,10 +20415,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3497</v>
+        <v>3475</v>
       </c>
       <c r="C7" t="s">
-        <v>3504</v>
+        <v>3482</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -20452,10 +20433,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3498</v>
+        <v>3476</v>
       </c>
       <c r="C8" t="s">
-        <v>3505</v>
+        <v>3483</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -20470,10 +20451,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>3506</v>
+        <v>3484</v>
       </c>
       <c r="C9" t="s">
-        <v>3514</v>
+        <v>3492</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -20484,10 +20465,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>3507</v>
+        <v>3485</v>
       </c>
       <c r="C10" t="s">
-        <v>3515</v>
+        <v>3493</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -20498,10 +20479,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3508</v>
+        <v>3486</v>
       </c>
       <c r="C11" t="s">
-        <v>3517</v>
+        <v>3495</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -20512,10 +20493,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3509</v>
+        <v>3487</v>
       </c>
       <c r="C12" t="s">
-        <v>3518</v>
+        <v>3496</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -20526,7 +20507,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3510</v>
+        <v>3488</v>
       </c>
       <c r="C13" t="s">
         <v>1547</v>
@@ -20540,7 +20521,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3511</v>
+        <v>3489</v>
       </c>
       <c r="C14" t="s">
         <v>1548</v>
@@ -20554,7 +20535,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3512</v>
+        <v>3490</v>
       </c>
       <c r="C15" t="s">
         <v>1148</v>
@@ -20568,7 +20549,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3513</v>
+        <v>3491</v>
       </c>
       <c r="C16" t="s">
         <v>1152</v>
@@ -20582,10 +20563,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>3519</v>
+        <v>3497</v>
       </c>
       <c r="C17" t="s">
-        <v>3521</v>
+        <v>3499</v>
       </c>
       <c r="G17">
         <v>12</v>
@@ -20596,10 +20577,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>3520</v>
+        <v>3498</v>
       </c>
       <c r="C18" t="s">
-        <v>3522</v>
+        <v>3500</v>
       </c>
       <c r="G18">
         <v>14</v>
@@ -30362,16 +30343,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3319</v>
+        <v>3297</v>
       </c>
       <c r="C5" t="s">
-        <v>3320</v>
+        <v>3298</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="G5">
         <v>19</v>
@@ -30382,16 +30363,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3321</v>
+        <v>3299</v>
       </c>
       <c r="C6" t="s">
-        <v>3322</v>
+        <v>3300</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="G6">
         <v>20</v>
@@ -30402,16 +30383,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3329</v>
+        <v>3307</v>
       </c>
       <c r="C7" t="s">
-        <v>3330</v>
+        <v>3308</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -30425,16 +30406,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3323</v>
+        <v>3301</v>
       </c>
       <c r="C8" t="s">
-        <v>3331</v>
+        <v>3309</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -30448,16 +30429,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3325</v>
+        <v>3303</v>
       </c>
       <c r="C9" t="s">
-        <v>3326</v>
+        <v>3304</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="G9">
         <v>23</v>
@@ -30468,13 +30449,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3327</v>
+        <v>3305</v>
       </c>
       <c r="C10" t="s">
-        <v>3328</v>
+        <v>3306</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E10" s="4"/>
       <c r="G10">
@@ -30504,13 +30485,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3332</v>
+        <v>3310</v>
       </c>
       <c r="C12" t="s">
-        <v>3333</v>
+        <v>3311</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E12" s="4"/>
       <c r="G12">
@@ -30522,16 +30503,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3334</v>
+        <v>3312</v>
       </c>
       <c r="C13" t="s">
-        <v>3335</v>
+        <v>3313</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -30545,16 +30526,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3336</v>
+        <v>3314</v>
       </c>
       <c r="C14" t="s">
-        <v>3337</v>
+        <v>3315</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -30568,13 +30549,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3338</v>
+        <v>3316</v>
       </c>
       <c r="C15" t="s">
-        <v>3339</v>
+        <v>3317</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E15" s="4"/>
       <c r="G15">
@@ -30586,13 +30567,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3340</v>
+        <v>3318</v>
       </c>
       <c r="C16" t="s">
-        <v>3341</v>
+        <v>3319</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E16" s="4"/>
       <c r="G16">
@@ -30604,13 +30585,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3342</v>
+        <v>3320</v>
       </c>
       <c r="C17" t="s">
-        <v>3346</v>
+        <v>3324</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E17" s="4"/>
       <c r="G17">
@@ -30622,13 +30603,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3343</v>
+        <v>3321</v>
       </c>
       <c r="C18" t="s">
-        <v>3347</v>
+        <v>3325</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E18" s="4"/>
       <c r="G18">
@@ -30640,13 +30621,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3344</v>
+        <v>3322</v>
       </c>
       <c r="C19" t="s">
-        <v>3348</v>
+        <v>3326</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E19" s="4"/>
       <c r="G19">
@@ -30658,13 +30639,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3360</v>
+        <v>3338</v>
       </c>
       <c r="C20" t="s">
-        <v>3361</v>
+        <v>3339</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E20" s="4"/>
       <c r="G20">
@@ -30676,13 +30657,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3345</v>
+        <v>3323</v>
       </c>
       <c r="C21" t="s">
-        <v>3349</v>
+        <v>3327</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E21" s="4"/>
       <c r="G21">
@@ -30694,13 +30675,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3350</v>
+        <v>3328</v>
       </c>
       <c r="C22" t="s">
-        <v>3351</v>
+        <v>3329</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E22" s="4"/>
       <c r="G22">
@@ -30712,16 +30693,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3352</v>
+        <v>3330</v>
       </c>
       <c r="C23" t="s">
-        <v>3354</v>
+        <v>3332</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -30735,16 +30716,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3353</v>
+        <v>3331</v>
       </c>
       <c r="C24" t="s">
-        <v>3355</v>
+        <v>3333</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -30758,13 +30739,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3356</v>
+        <v>3334</v>
       </c>
       <c r="C25" t="s">
-        <v>3359</v>
+        <v>3337</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" t="b">
@@ -30779,13 +30760,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3357</v>
+        <v>3335</v>
       </c>
       <c r="C26" t="s">
-        <v>3358</v>
+        <v>3336</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E26" s="4"/>
       <c r="G26">
@@ -30797,16 +30778,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3362</v>
+        <v>3340</v>
       </c>
       <c r="C27" t="s">
-        <v>3364</v>
+        <v>3342</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -30820,16 +30801,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3363</v>
+        <v>3341</v>
       </c>
       <c r="C28" t="s">
-        <v>3365</v>
+        <v>3343</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -30843,13 +30824,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3366</v>
+        <v>3344</v>
       </c>
       <c r="C29" t="s">
-        <v>3367</v>
+        <v>3345</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E29" s="4"/>
       <c r="G29">
@@ -30861,13 +30842,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>3368</v>
+        <v>3346</v>
       </c>
       <c r="C30" t="s">
-        <v>3369</v>
+        <v>3347</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" t="b">
@@ -30882,13 +30863,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3370</v>
+        <v>3348</v>
       </c>
       <c r="C31" t="s">
-        <v>3371</v>
+        <v>3349</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>3324</v>
+        <v>3302</v>
       </c>
       <c r="E31" s="4"/>
       <c r="G31">
@@ -30903,7 +30884,7 @@
         <v>888</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>3372</v>
+        <v>3350</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -30916,7 +30897,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>3373</v>
+        <v>3351</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>26</v>
@@ -30936,7 +30917,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>3374</v>
+        <v>3352</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>27</v>
@@ -30956,7 +30937,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>3375</v>
+        <v>3353</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>28</v>
@@ -30976,7 +30957,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>3376</v>
+        <v>3354</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>29</v>
@@ -30996,7 +30977,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>3377</v>
+        <v>3355</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
@@ -31016,7 +30997,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>3378</v>
+        <v>3356</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>31</v>
@@ -31039,7 +31020,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>3379</v>
+        <v>3357</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>32</v>
@@ -31056,7 +31037,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>3380</v>
+        <v>3358</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>1308</v>
@@ -31074,7 +31055,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>3381</v>
+        <v>3359</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>1309</v>
@@ -31090,7 +31071,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>3382</v>
+        <v>3360</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>1310</v>
@@ -31108,7 +31089,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>3383</v>
+        <v>3361</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>1311</v>
@@ -31124,7 +31105,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>3384</v>
+        <v>3362</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>1312</v>
@@ -31142,7 +31123,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>3385</v>
+        <v>3363</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>1313</v>
@@ -34371,16 +34352,16 @@
         <v>881</v>
       </c>
       <c r="H1" t="s">
-        <v>3315</v>
+        <v>3293</v>
       </c>
       <c r="I1" t="s">
-        <v>3316</v>
+        <v>3294</v>
       </c>
       <c r="J1" t="s">
-        <v>3317</v>
+        <v>3295</v>
       </c>
       <c r="K1" t="s">
-        <v>3318</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
@@ -38444,10 +38425,10 @@
         <v>144</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>3501</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>3278</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>3293</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>22</v>
@@ -38467,10 +38448,10 @@
         <v>145</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>3502</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>3279</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>3294</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>22</v>
@@ -38490,10 +38471,10 @@
         <v>146</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>3503</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>3280</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>3295</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>22</v>
@@ -38516,10 +38497,10 @@
         <v>147</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>3504</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>3281</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>3296</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>22</v>
@@ -38542,10 +38523,10 @@
         <v>148</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>3505</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>3282</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>3297</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>22</v>
@@ -38565,10 +38546,10 @@
         <v>149</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>3506</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>3283</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>3298</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>22</v>
@@ -38591,10 +38572,10 @@
         <v>150</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>3507</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>3284</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>3299</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>22</v>
@@ -38614,10 +38595,10 @@
         <v>151</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>3508</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>3285</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>3300</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>22</v>
@@ -38640,10 +38621,10 @@
         <v>152</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>3509</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>3286</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>3301</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>22</v>
@@ -38663,10 +38644,10 @@
         <v>153</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>3510</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>3287</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>3302</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>22</v>
@@ -38689,10 +38670,10 @@
         <v>154</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>3511</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>3288</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>3303</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>22</v>
@@ -38712,10 +38693,10 @@
         <v>155</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>3512</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>3289</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>3304</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>22</v>
@@ -38735,10 +38716,10 @@
         <v>156</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>3513</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>3290</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>3305</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>22</v>
@@ -38758,10 +38739,10 @@
         <v>157</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>3514</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>3291</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>3306</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>22</v>
@@ -38781,10 +38762,10 @@
         <v>158</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>3515</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>3292</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>3307</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>22</v>
@@ -39983,7 +39964,7 @@
         <v>198</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>3308</v>
+        <v>3516</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>681</v>
@@ -40009,7 +39990,7 @@
         <v>199</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>3309</v>
+        <v>3517</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>682</v>
@@ -40035,7 +40016,7 @@
         <v>200</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>3310</v>
+        <v>3518</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>684</v>
@@ -40058,7 +40039,7 @@
         <v>201</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>3311</v>
+        <v>3519</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>686</v>
@@ -40690,7 +40671,7 @@
         <v>221</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>3312</v>
+        <v>3520</v>
       </c>
       <c r="C223" s="13" t="s">
         <v>701</v>
@@ -40716,7 +40697,7 @@
         <v>222</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>3313</v>
+        <v>3521</v>
       </c>
       <c r="C224" s="13" t="s">
         <v>702</v>
@@ -40742,7 +40723,7 @@
         <v>223</v>
       </c>
       <c r="B225" s="14" t="s">
-        <v>3314</v>
+        <v>3522</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>703</v>
@@ -53354,10 +53335,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3386</v>
+        <v>3364</v>
       </c>
       <c r="C3" t="s">
-        <v>3393</v>
+        <v>3371</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -53372,10 +53353,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3387</v>
+        <v>3365</v>
       </c>
       <c r="C4" t="s">
-        <v>3394</v>
+        <v>3372</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -53392,10 +53373,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3388</v>
+        <v>3366</v>
       </c>
       <c r="C5" t="s">
-        <v>3396</v>
+        <v>3374</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -53412,10 +53393,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3392</v>
+        <v>3370</v>
       </c>
       <c r="C6" t="s">
-        <v>3395</v>
+        <v>3373</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -53432,10 +53413,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3389</v>
+        <v>3367</v>
       </c>
       <c r="C7" t="s">
-        <v>3397</v>
+        <v>3375</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -53452,7 +53433,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3390</v>
+        <v>3368</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -53472,10 +53453,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3391</v>
+        <v>3369</v>
       </c>
       <c r="C9" t="s">
-        <v>3398</v>
+        <v>3376</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B131E8-8D2B-440F-AFDF-7C82A45ABE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEF8065-9495-4BBC-A4BC-C6A85EBA78A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="5" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="2250" yWindow="1005" windowWidth="34725" windowHeight="18735" firstSheet="10" activeTab="13" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="CherryAugment_header" sheetId="36" r:id="rId11"/>
     <sheet name="SwarmAugment_header" sheetId="37" r:id="rId12"/>
     <sheet name="KiwiAugment_header" sheetId="6" r:id="rId13"/>
-    <sheet name="KiwiAumgentSet_header" sheetId="35" r:id="rId14"/>
+    <sheet name="KiwiAugmentSet_header" sheetId="35" r:id="rId14"/>
     <sheet name="anvil_header" sheetId="11" r:id="rId15"/>
     <sheet name="GoH_header" sheetId="40" r:id="rId16"/>
     <sheet name="TFTSet_header" sheetId="15" r:id="rId17"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6865" uniqueCount="3523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6972" uniqueCount="3571">
   <si>
     <t>key</t>
   </si>
@@ -12597,6 +12597,173 @@
   </si>
   <si>
     <t>secondaryAbilityResource baseValue baseValue</t>
+  </si>
+  <si>
+    <t>{3696d198} {c4182067}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {231af825}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {c98a82ca}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {05835d27}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息描述部分键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息追踪部分键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>满级效果详细信息键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>满级效果简介键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {c4182067}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {c4182067}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {c4182067}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {c4182067}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3696d198} {231af825}_content_zh</t>
+  </si>
+  <si>
+    <t>{3696d198} {231af825}_content_zh_burn</t>
+  </si>
+  <si>
+    <t>{3696d198} {231af825}_content_en</t>
+  </si>
+  <si>
+    <t>{3696d198} {231af825}_content_en_burn</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {c98a82ca}_content_zh</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {c98a82ca}_content_zh_burn</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {c98a82ca}_content_en</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {c98a82ca}_content_en_burn</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {05835d27}_content_zh</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {05835d27}_content_zh_burn</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {05835d27}_content_en</t>
+  </si>
+  <si>
+    <t>{791eb92e} {5753a320} {05835d27}_content_en_burn</t>
+  </si>
+  <si>
+    <t>强化符文详细信息描述部分（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息描述部分（中文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息描述部分（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息描述部分（英文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文详细信息追踪部分（中文）</t>
+  </si>
+  <si>
+    <t>强化符文详细信息追踪部分（中文/数值转换）</t>
+  </si>
+  <si>
+    <t>强化符文详细信息追踪部分（英文）</t>
+  </si>
+  <si>
+    <t>强化符文详细信息追踪部分（英文/数值转换）</t>
+  </si>
+  <si>
+    <t>满级效果简介（中文）</t>
+  </si>
+  <si>
+    <t>满级效果简介（中文/数值转换）</t>
+  </si>
+  <si>
+    <t>满级效果简介（英文）</t>
+  </si>
+  <si>
+    <t>满级效果简介（英文/数值转换）</t>
+  </si>
+  <si>
+    <t>满级效果详细信息（中文）</t>
+  </si>
+  <si>
+    <t>满级效果详细信息（中文/数值转换）</t>
+  </si>
+  <si>
+    <t>满级效果详细信息（英文）</t>
+  </si>
+  <si>
+    <t>满级效果详细信息（英文/数值转换）</t>
+  </si>
+  <si>
+    <t>defaultValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceResolver</t>
+  </si>
+  <si>
+    <t>ResourceResolver resourceMap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源解析器主键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源解析器映射字典</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{40c7b66f}_object</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17828,16 +17995,16 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEC55FC-26A9-4869-A0C1-950FCC7DF8BC}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
+    <col min="5" max="6" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -17854,10 +18021,13 @@
         <v>23</v>
       </c>
       <c r="F1" t="s">
+        <v>3563</v>
+      </c>
+      <c r="G1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -17870,11 +18040,11 @@
       <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -17887,11 +18057,11 @@
       <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -17907,11 +18077,11 @@
       <c r="E4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -17924,11 +18094,11 @@
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -17941,11 +18111,11 @@
       <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -17958,11 +18128,11 @@
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -17975,11 +18145,11 @@
       <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -17995,11 +18165,11 @@
       <c r="E9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -18015,287 +18185,599 @@
       <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>465</v>
+        <v>3523</v>
       </c>
       <c r="C11" t="s">
-        <v>466</v>
+        <v>3527</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>453</v>
+        <v>3524</v>
       </c>
       <c r="C12" t="s">
-        <v>454</v>
+        <v>3528</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>455</v>
+        <v>3525</v>
       </c>
       <c r="C13" t="s">
-        <v>456</v>
+        <v>3530</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>457</v>
+        <v>3526</v>
       </c>
       <c r="C14" t="s">
-        <v>458</v>
+        <v>3529</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>467</v>
+      <c r="B16" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="C16" t="s">
-        <v>474</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>470</v>
+      <c r="B17" s="1" t="s">
+        <v>455</v>
       </c>
       <c r="C17" t="s">
-        <v>475</v>
-      </c>
-      <c r="F17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>468</v>
+      <c r="B18" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="C18" t="s">
-        <v>476</v>
-      </c>
-      <c r="F18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="C19" t="s">
-        <v>482</v>
-      </c>
-      <c r="F19">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>3273</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>471</v>
+      <c r="B20" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="C20" t="s">
-        <v>477</v>
-      </c>
-      <c r="F20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>464</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C21" t="s">
-        <v>484</v>
-      </c>
-      <c r="F21">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C22" t="s">
-        <v>478</v>
-      </c>
-      <c r="F22">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="C23" t="s">
-        <v>487</v>
-      </c>
-      <c r="F23">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+      <c r="G23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C24" t="s">
-        <v>473</v>
-      </c>
-      <c r="F24">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+      <c r="G24">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C25" t="s">
-        <v>488</v>
-      </c>
-      <c r="F25">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+      <c r="G25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="C26" t="s">
-        <v>463</v>
-      </c>
-      <c r="F26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+      <c r="G26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C27" t="s">
-        <v>461</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C28" t="s">
+        <v>487</v>
+      </c>
+      <c r="G28">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C29" t="s">
+        <v>473</v>
+      </c>
+      <c r="G29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C30" t="s">
+        <v>488</v>
+      </c>
+      <c r="G30">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>3531</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3547</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3548</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3549</v>
+      </c>
+      <c r="G33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3550</v>
+      </c>
+      <c r="G34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3551</v>
+      </c>
+      <c r="G35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3536</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3552</v>
+      </c>
+      <c r="G36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3537</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3553</v>
+      </c>
+      <c r="G37">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3554</v>
+      </c>
+      <c r="G38">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3555</v>
+      </c>
+      <c r="G39">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3540</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3556</v>
+      </c>
+      <c r="G40">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3541</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3557</v>
+      </c>
+      <c r="G41">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3542</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3558</v>
+      </c>
+      <c r="G42">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3543</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3559</v>
+      </c>
+      <c r="G43">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3560</v>
+      </c>
+      <c r="G44">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3561</v>
+      </c>
+      <c r="G45">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3562</v>
+      </c>
+      <c r="G46">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C47" t="s">
+        <v>463</v>
+      </c>
+      <c r="G47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C48" t="s">
+        <v>461</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C49" t="s">
         <v>480</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28">
-        <v>24</v>
+      <c r="D49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G49">
+    <sortCondition ref="A1:A49"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18717,16 +19199,16 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889E42AC-5584-44B0-BFBD-399F3EB60349}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
+    <col min="5" max="6" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -18743,10 +19225,13 @@
         <v>23</v>
       </c>
       <c r="F1" t="s">
+        <v>3564</v>
+      </c>
+      <c r="G1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -18759,11 +19244,11 @@
       <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -18776,11 +19261,11 @@
       <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -18796,11 +19281,14 @@
       <c r="E4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -18813,11 +19301,11 @@
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -18830,11 +19318,11 @@
       <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -18847,11 +19335,11 @@
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -18864,11 +19352,11 @@
       <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F8">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -18881,11 +19369,11 @@
       <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -18901,11 +19389,11 @@
       <c r="E10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -18921,365 +19409,700 @@
       <c r="E11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>465</v>
+        <v>3523</v>
       </c>
       <c r="C12" t="s">
-        <v>466</v>
+        <v>3527</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>453</v>
+        <v>3524</v>
       </c>
       <c r="C13" t="s">
-        <v>454</v>
+        <v>3528</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F13">
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>455</v>
+        <v>3525</v>
       </c>
       <c r="C14" t="s">
-        <v>456</v>
+        <v>3530</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>457</v>
+        <v>3526</v>
       </c>
       <c r="C15" t="s">
-        <v>458</v>
+        <v>3529</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3273</v>
+        <v>465</v>
+      </c>
+      <c r="C16" t="s">
+        <v>466</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C17" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>467</v>
+      <c r="B18" s="1" t="s">
+        <v>455</v>
       </c>
       <c r="C18" t="s">
-        <v>474</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>470</v>
+      <c r="B19" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="C19" t="s">
-        <v>475</v>
-      </c>
-      <c r="F19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="C20" t="s">
-        <v>476</v>
-      </c>
-      <c r="F20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>481</v>
+      <c r="B21" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="C21" t="s">
-        <v>482</v>
-      </c>
-      <c r="F21">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>464</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>471</v>
+      <c r="B22" s="1" t="s">
+        <v>3565</v>
       </c>
       <c r="C22" t="s">
-        <v>477</v>
-      </c>
-      <c r="F22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>3567</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="G22">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C23" t="s">
-        <v>484</v>
-      </c>
-      <c r="F23">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C24" t="s">
-        <v>478</v>
-      </c>
-      <c r="F24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="C25" t="s">
-        <v>487</v>
-      </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+      <c r="G25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C26" t="s">
-        <v>473</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+      <c r="G26">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C27" t="s">
-        <v>488</v>
-      </c>
-      <c r="F27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="C28" t="s">
-        <v>463</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+      <c r="G28">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C29" t="s">
-        <v>461</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+      <c r="G29">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C30" t="s">
-        <v>480</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+      <c r="G30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>3276</v>
+        <v>472</v>
       </c>
       <c r="C31" t="s">
-        <v>3277</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>3267</v>
+        <v>486</v>
       </c>
       <c r="C32" t="s">
-        <v>3266</v>
-      </c>
-      <c r="F32">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>3268</v>
+        <v>3531</v>
       </c>
       <c r="C33" t="s">
-        <v>3270</v>
-      </c>
-      <c r="F33">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+        <v>3547</v>
+      </c>
+      <c r="G33">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>3532</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3548</v>
+      </c>
+      <c r="G34">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3533</v>
+      </c>
+      <c r="C35" t="s">
+        <v>3549</v>
+      </c>
+      <c r="G35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C36" t="s">
+        <v>3550</v>
+      </c>
+      <c r="G36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3535</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3551</v>
+      </c>
+      <c r="G37">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3536</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3552</v>
+      </c>
+      <c r="G38">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3537</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3553</v>
+      </c>
+      <c r="G39">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3538</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3554</v>
+      </c>
+      <c r="G40">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3539</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3555</v>
+      </c>
+      <c r="G41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3540</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3556</v>
+      </c>
+      <c r="G42">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3541</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3557</v>
+      </c>
+      <c r="G43">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3542</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3558</v>
+      </c>
+      <c r="G44">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3543</v>
+      </c>
+      <c r="C45" t="s">
+        <v>3559</v>
+      </c>
+      <c r="G45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3544</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3560</v>
+      </c>
+      <c r="G46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>3545</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3561</v>
+      </c>
+      <c r="G47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3562</v>
+      </c>
+      <c r="G48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C49" t="s">
+        <v>463</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C50" t="s">
+        <v>461</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C51" t="s">
+        <v>480</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>3276</v>
+      </c>
+      <c r="C52" t="s">
+        <v>3277</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3267</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3266</v>
+      </c>
+      <c r="G53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3270</v>
+      </c>
+      <c r="G54">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>3269</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C55" t="s">
         <v>3271</v>
       </c>
-      <c r="F34">
+      <c r="G55">
         <v>13</v>
       </c>
     </row>
+    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>3566</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3568</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="G56">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
-    <sortCondition ref="A1:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G56">
+    <sortCondition ref="A1:A56"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19289,7 +20112,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BF9C7C-6735-47CD-AD6E-C4479D5531D4}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="49.375" bestFit="1" customWidth="1"/>
@@ -19368,7 +20191,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19460,7 +20283,7 @@
         <v>22</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19480,23 +20303,25 @@
         <v>22</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>3233</v>
+      <c r="B11" s="1" t="s">
+        <v>3274</v>
       </c>
       <c r="C11" t="s">
-        <v>3235</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>3275</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>3569</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19504,15 +20329,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="C12" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19520,15 +20345,15 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3237</v>
+        <v>3234</v>
       </c>
       <c r="C13" t="s">
-        <v>3241</v>
+        <v>3236</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19536,15 +20361,15 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="C14" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19552,15 +20377,15 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C15" t="s">
-        <v>3245</v>
+        <v>3242</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19568,15 +20393,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="C16" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19584,15 +20409,15 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>3247</v>
+        <v>3240</v>
       </c>
       <c r="C17" t="s">
-        <v>3249</v>
+        <v>3246</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19600,15 +20425,15 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="C18" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19616,15 +20441,15 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>3232</v>
+        <v>3248</v>
       </c>
       <c r="C19" t="s">
-        <v>480</v>
+        <v>3250</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19632,15 +20457,15 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>3256</v>
+        <v>3232</v>
       </c>
       <c r="C20" t="s">
-        <v>3261</v>
+        <v>480</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19648,15 +20473,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="C21" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19664,15 +20489,15 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="C22" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19680,15 +20505,15 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="C23" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19696,15 +20521,15 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="C24" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -19712,26 +20537,52 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>3272</v>
+        <v>3260</v>
       </c>
       <c r="C25" t="s">
-        <v>3254</v>
+        <v>3265</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B26" s="6"/>
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>3570</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3277</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
+      <c r="F26">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B27" s="6"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3254</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="F27">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
@@ -19763,9 +20614,19 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
     </row>
+    <row r="34" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B34" s="6"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="6"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F25">
-    <sortCondition ref="A1:A25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F27">
+    <sortCondition ref="A1:A27"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEF8065-9495-4BBC-A4BC-C6A85EBA78A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9C789C-5A4F-4FBF-A2FC-414CD88B96F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="1005" windowWidth="34725" windowHeight="18735" firstSheet="10" activeTab="13" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="10" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -18077,6 +18077,9 @@
       <c r="E4" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>3</v>
       </c>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9C789C-5A4F-4FBF-A2FC-414CD88B96F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ECEC21-1801-4D66-86E9-364EFDB94B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="10" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6972" uniqueCount="3571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6980" uniqueCount="3575">
   <si>
     <t>key</t>
   </si>
@@ -12763,6 +12763,22 @@
   </si>
   <si>
     <t>{40c7b66f}_object</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{815dad28}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大等级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RootSpell mSpell DataValues MaxLevel</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -17995,10 +18011,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAEC55FC-26A9-4869-A0C1-950FCC7DF8BC}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="4"/>
@@ -18115,7 +18131,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18132,7 +18148,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18149,7 +18165,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18169,7 +18185,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18189,7 +18205,7 @@
         <v>22</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18206,7 +18222,7 @@
         <v>22</v>
       </c>
       <c r="G11">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18226,7 +18242,7 @@
         <v>22</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18243,7 +18259,7 @@
         <v>22</v>
       </c>
       <c r="G13">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18260,7 +18276,7 @@
         <v>22</v>
       </c>
       <c r="G14">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18277,7 +18293,7 @@
         <v>22</v>
       </c>
       <c r="G15">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18294,7 +18310,7 @@
         <v>22</v>
       </c>
       <c r="G16">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18302,16 +18318,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C17" t="s">
-        <v>456</v>
+        <v>3571</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>22</v>
+        <v>3572</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>3572</v>
       </c>
       <c r="G17">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18319,19 +18335,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C18" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G18">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18339,13 +18352,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3273</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
+        <v>457</v>
+      </c>
+      <c r="C19" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18353,30 +18372,36 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C20" t="s">
-        <v>464</v>
+        <v>3273</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>22</v>
+        <v>3572</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>3572</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>467</v>
+      <c r="B21" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="C21" t="s">
-        <v>474</v>
+        <v>464</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18384,13 +18409,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C22" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18398,13 +18423,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C23" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G23">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18412,13 +18437,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="C24" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G24">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18426,13 +18451,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="C25" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18440,13 +18465,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C26" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G26">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18454,10 +18479,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="C27" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="G27">
         <v>20</v>
@@ -18468,13 +18493,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C28" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="G28">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18482,13 +18507,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="C29" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="G29">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18496,13 +18521,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="C30" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="G30">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18510,10 +18535,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>3531</v>
+        <v>486</v>
       </c>
       <c r="C31" t="s">
-        <v>3547</v>
+        <v>488</v>
       </c>
       <c r="G31">
         <v>25</v>
@@ -18524,13 +18549,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="C32" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="G32">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18538,13 +18563,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="C33" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="G33">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18552,13 +18577,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="C34" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="G34">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18566,10 +18591,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="C35" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="G35">
         <v>30</v>
@@ -18580,13 +18605,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="C36" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="G36">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18594,13 +18619,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="C37" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="G37">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18608,13 +18633,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="C38" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="G38">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18622,10 +18647,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="C39" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="G39">
         <v>35</v>
@@ -18636,13 +18661,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="C40" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="G40">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18650,13 +18675,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="C41" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="G41">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18664,13 +18689,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="C42" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="G42">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18678,10 +18703,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="C43" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="G43">
         <v>40</v>
@@ -18692,13 +18717,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="C44" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="G44">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18706,13 +18731,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="C45" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="G45">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18720,13 +18745,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="C46" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="G46">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18734,13 +18759,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>462</v>
+        <v>3546</v>
       </c>
       <c r="C47" t="s">
-        <v>463</v>
+        <v>3562</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18748,16 +18773,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C48" t="s">
-        <v>461</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="G48">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18765,21 +18787,55 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C49" t="s">
+        <v>461</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>480</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49">
-        <v>45</v>
+      <c r="D50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>3574</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3573</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>3572</v>
+      </c>
+      <c r="G51">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G49">
-    <sortCondition ref="A1:A49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
+    <sortCondition ref="A1:A51"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B866FC54-5427-449E-ADDE-398CE14C0A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B108B7-11D6-4A12-9F5C-637D3C89544D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="1695" windowWidth="34725" windowHeight="18735" firstSheet="12" activeTab="18" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="2595" yWindow="1350" windowWidth="34725" windowHeight="18735" firstSheet="12" activeTab="15" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7071" uniqueCount="3613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7097" uniqueCount="3634">
   <si>
     <t>key</t>
   </si>
@@ -12934,6 +12934,90 @@
   </si>
   <si>
     <t>阶段名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>key1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主键1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色文件夹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{b0f32561}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可用回合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>key2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主键2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enabled</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可用性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkinID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮肤序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>互斥荣誉嘉宾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>互斥荣誉嘉宾姓名（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>互斥荣誉嘉宾姓名（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{e7879fb5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{e7879fb5} Subtitle_contents_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{e7879fb5} Subtitle_contents_en</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -13117,7 +13201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13287,15 +13371,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -21376,11 +21451,11 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF611F9-13A5-4CF6-B8E3-E0A2C9AC1592}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21412,14 +21487,12 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>3613</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>3614</v>
+      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="G2">
         <v>0</v>
@@ -21430,17 +21503,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3477</v>
+        <v>3621</v>
       </c>
       <c r="C3" t="s">
-        <v>3481</v>
+        <v>3622</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>22</v>
+        <v>3625</v>
       </c>
       <c r="E3" s="4"/>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21448,17 +21521,17 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3478</v>
+        <v>3615</v>
       </c>
       <c r="C4" t="s">
-        <v>3494</v>
+        <v>3616</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="4"/>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21466,17 +21539,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3479</v>
+        <v>3623</v>
       </c>
       <c r="C5" t="s">
-        <v>2891</v>
+        <v>3624</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>3625</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>3625</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
       <c r="G5">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21484,17 +21562,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3480</v>
+        <v>3626</v>
       </c>
       <c r="C6" t="s">
-        <v>1082</v>
+        <v>3627</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4"/>
+        <v>3625</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>3625</v>
+      </c>
       <c r="G6">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21502,17 +21582,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3475</v>
+        <v>3617</v>
       </c>
       <c r="C7" t="s">
-        <v>3482</v>
+        <v>3618</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="4"/>
       <c r="G7">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21520,162 +21600,316 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>3631</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3628</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>3625</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>3625</v>
+      </c>
+      <c r="G8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>3619</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3620</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3477</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>3481</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="G10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>3478</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3494</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="G11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3479</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="G12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3480</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="G13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3482</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="G14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>3476</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C15" s="2" t="s">
         <v>3483</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="G8">
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="G15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>3484</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>3492</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>3485</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>3493</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>3484</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3492</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>3485</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3493</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="B18" s="56" t="s">
         <v>3486</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C18" s="2" t="s">
         <v>3495</v>
       </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="G18">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="56" t="s">
         <v>3487</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C19" s="2" t="s">
         <v>3496</v>
       </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="G19">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="56" t="s">
         <v>3488</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C20" s="2" t="s">
         <v>1547</v>
       </c>
-      <c r="G13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="G20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="56" t="s">
         <v>3489</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C21" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="G14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="G21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="56" t="s">
         <v>3490</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C22" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="G15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="G22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>3491</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C23" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="G16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="G23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="56" t="s">
         <v>3497</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C24" s="2" t="s">
         <v>3499</v>
       </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="G24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="56" t="s">
         <v>3498</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C25" s="2" t="s">
         <v>3500</v>
       </c>
-      <c r="G18">
-        <v>14</v>
+      <c r="G25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="15">
+        <v>24</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>3632</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>3629</v>
+      </c>
+      <c r="G26">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="15">
+        <v>25</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>3633</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>3630</v>
+      </c>
+      <c r="G27">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
-    <sortCondition ref="A1:A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G27">
+    <sortCondition ref="A1:A27"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21921,13 +22155,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="57">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="6" t="s">
         <v>3609</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" t="s">
         <v>3610</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -21939,13 +22173,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="57">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="6" t="s">
         <v>3611</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" t="s">
         <v>3612</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -22066,13 +22300,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="57">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="1" t="s">
         <v>3586</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" t="s">
         <v>867</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -22083,13 +22317,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="57">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="1" t="s">
         <v>3587</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" t="s">
         <v>3598</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -22100,13 +22334,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="57">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="1" t="s">
         <v>3588</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" t="s">
         <v>3599</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -22117,13 +22351,13 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="57">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="1" t="s">
         <v>3589</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" t="s">
         <v>3600</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -22134,13 +22368,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="57">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="6" t="s">
         <v>3590</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" t="s">
         <v>868</v>
       </c>
       <c r="F8">
@@ -22148,13 +22382,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="57">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="6" t="s">
         <v>3591</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" t="s">
         <v>869</v>
       </c>
       <c r="F9">

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B108B7-11D6-4A12-9F5C-637D3C89544D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AA8B5-B45F-405F-9DAD-E36C8B787C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="1350" windowWidth="34725" windowHeight="18735" firstSheet="12" activeTab="15" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="3285" yWindow="2040" windowWidth="34725" windowHeight="18735" firstSheet="12" activeTab="16" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -29,27 +29,28 @@
     <sheet name="KiwiAugmentSet_header" sheetId="35" r:id="rId14"/>
     <sheet name="anvil_header" sheetId="11" r:id="rId15"/>
     <sheet name="GoH_header" sheetId="40" r:id="rId16"/>
-    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId17"/>
-    <sheet name="CherryRound_header" sheetId="43" r:id="rId18"/>
-    <sheet name="CherryPhase_header" sheetId="42" r:id="rId19"/>
-    <sheet name="TFTSet_header" sheetId="15" r:id="rId20"/>
-    <sheet name="TFTShop_header" sheetId="17" r:id="rId21"/>
-    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId22"/>
-    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId23"/>
-    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId24"/>
-    <sheet name="TFTRound_header" sheetId="19" r:id="rId25"/>
-    <sheet name="TFTPortal_header" sheetId="27" r:id="rId26"/>
-    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId27"/>
-    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId28"/>
-    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId29"/>
-    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId30"/>
-    <sheet name="TFTItemList_header" sheetId="22" r:id="rId31"/>
-    <sheet name="TFTItem_header" sheetId="23" r:id="rId32"/>
-    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId33"/>
-    <sheet name="TFTTrait_header" sheetId="25" r:id="rId34"/>
-    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId35"/>
-    <sheet name="TFTScript_header" sheetId="26" r:id="rId36"/>
-    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId37"/>
+    <sheet name="cameo_header" sheetId="44" r:id="rId17"/>
+    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId18"/>
+    <sheet name="CherryRound_header" sheetId="43" r:id="rId19"/>
+    <sheet name="CherryPhase_header" sheetId="42" r:id="rId20"/>
+    <sheet name="TFTSet_header" sheetId="15" r:id="rId21"/>
+    <sheet name="TFTShop_header" sheetId="17" r:id="rId22"/>
+    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId23"/>
+    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId24"/>
+    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId25"/>
+    <sheet name="TFTRound_header" sheetId="19" r:id="rId26"/>
+    <sheet name="TFTPortal_header" sheetId="27" r:id="rId27"/>
+    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId28"/>
+    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId29"/>
+    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId30"/>
+    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId31"/>
+    <sheet name="TFTItemList_header" sheetId="22" r:id="rId32"/>
+    <sheet name="TFTItem_header" sheetId="23" r:id="rId33"/>
+    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId34"/>
+    <sheet name="TFTTrait_header" sheetId="25" r:id="rId35"/>
+    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId36"/>
+    <sheet name="TFTScript_header" sheetId="26" r:id="rId37"/>
+    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$341</definedName>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7097" uniqueCount="3634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7140" uniqueCount="3648">
   <si>
     <t>key</t>
   </si>
@@ -13018,6 +13019,62 @@
   </si>
   <si>
     <t>{e7879fb5} Subtitle_contents_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{f426fde9}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{f426fde9}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{f426fde9}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{f426fde9}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3942d706}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3942d706}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{be8164b4}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{be8164b4}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{f426fde9}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3942d706}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{be8164b4}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄文件夹加密字符串</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChampionNameHash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>championName</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -21917,6 +21974,273 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656E066B-CAF0-4A5E-8BA4-5ACC1ECD3D32}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>881</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3647</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3646</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3644</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3481</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3643</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>3641</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3492</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3640</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3493</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3639</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2908</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3638</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2909</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>3637</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>3636</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>3635</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3499</v>
+      </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3634</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3500</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8A9EE-70FA-478F-A3B9-CC27898022D4}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22088,7 +22412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D5B4D1-ED3B-471D-986E-326D93CEBEDE}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22226,308 +22550,6 @@
       <c r="B16" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916B8D1A-71B4-46F4-B386-907D3EE40FC6}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3585</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3602</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3586</v>
-      </c>
-      <c r="C4" t="s">
-        <v>867</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3587</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3598</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3588</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3599</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3589</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3600</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>3590</v>
-      </c>
-      <c r="C8" t="s">
-        <v>868</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>3591</v>
-      </c>
-      <c r="C9" t="s">
-        <v>869</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>3592</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>2956</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>3593</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>3601</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>3594</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>3603</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>3595</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>3604</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>3596</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>3605</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>3597</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>3606</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="6"/>
-    </row>
-    <row r="17" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B18" s="6"/>
-    </row>
-    <row r="19" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B19" s="6"/>
-    </row>
-    <row r="20" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B20" s="6"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F15">
-    <sortCondition ref="A1:A15"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22732,6 +22754,308 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916B8D1A-71B4-46F4-B386-907D3EE40FC6}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3602</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C4" t="s">
+        <v>867</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3587</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3598</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3588</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3599</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3589</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3600</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>3590</v>
+      </c>
+      <c r="C8" t="s">
+        <v>868</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>3591</v>
+      </c>
+      <c r="C9" t="s">
+        <v>869</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3592</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>3593</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3601</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3603</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3595</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3604</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3596</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3605</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>3597</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3606</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+    </row>
+    <row r="19" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+    </row>
+    <row r="20" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F15">
+    <sortCondition ref="A1:A15"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3901968F-E5DF-4CBD-ADFB-08FA8A3F4044}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G299"/>
@@ -27014,7 +27338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40963FC-D1AF-47E5-BB09-9770285565C2}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G27"/>
@@ -27514,7 +27838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEED51C0-16CE-493B-ACDF-CED633B09365}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:G8"/>
@@ -27677,7 +28001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6ED802-F57E-44A6-B120-12D8C7BE7DFE}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G9"/>
@@ -27820,7 +28144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:G10"/>
@@ -27984,7 +28308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G68"/>
@@ -29341,7 +29665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B1F2EF-0DC6-4BB2-8172-4E4198527108}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:G28"/>
@@ -29832,7 +30156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:G10"/>
@@ -30020,7 +30344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:G17"/>
@@ -30339,227 +30663,6 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
     <sortCondition ref="A1:A17"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
-  <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2439</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2433</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>3015</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3016</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>3015</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>3015</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3013</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3014</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>3015</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2440</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2434</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2441</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2435</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2436</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2437</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2443</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2438</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
-    <sortCondition ref="A1:A10"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31483,6 +31586,227 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
+  <sheetPr codeName="Sheet12"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2437</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
+    <sortCondition ref="A1:A10"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78003282-BF12-4B9E-88E0-0647BA982AE8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G29"/>
@@ -31960,7 +32284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8BF486-9605-4C14-9D33-B85EFC67F833}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G11"/>
@@ -32142,7 +32466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF0C918-C1C4-4CA0-AE17-312A0FD1DCCE}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:G51"/>
@@ -33099,7 +33423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC122C9-2D95-4069-BA3C-DDFB1C7F608D}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:G11"/>
@@ -33264,7 +33588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:G22"/>
@@ -33653,7 +33977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:G13"/>
@@ -33901,7 +34225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EAFC06-5BD2-40F9-AAC9-8F399DCA30B2}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:G10"/>
@@ -34042,7 +34366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:G10"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8AA8B5-B45F-405F-9DAD-E36C8B787C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8FF65B-8765-4B26-9217-24F2568E2396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2040" windowWidth="34725" windowHeight="18735" firstSheet="12" activeTab="16" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="37" activeTab="43" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -51,6 +51,12 @@
     <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId36"/>
     <sheet name="TFTScript_header" sheetId="26" r:id="rId37"/>
     <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId38"/>
+    <sheet name="fontDesc_header" sheetId="45" r:id="rId39"/>
+    <sheet name="fontType_header" sheetId="46" r:id="rId40"/>
+    <sheet name="fontResolution_header" sheetId="47" r:id="rId41"/>
+    <sheet name="fontStyle_header" sheetId="48" r:id="rId42"/>
+    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId43"/>
+    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId44"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$341</definedName>
@@ -76,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7140" uniqueCount="3648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7340" uniqueCount="3719">
   <si>
     <t>key</t>
   </si>
@@ -13075,6 +13081,290 @@
   </si>
   <si>
     <t>championName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>typeData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolutionData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Color</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlineColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>glowColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelectionBoxColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>colorblindColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>colorblindOutlineColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fillTextureName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>字体类型键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>字体分辨率键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轮廓颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴影颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发光颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择框颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>色盲模式颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>色盲模式轮廓颜色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>填充纹理名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>localeName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mFontFilePath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FontFilePathBold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>字体文件路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粗体文件路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>autoScale</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动缩放</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>localeResolution_index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resolution_index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>screenHeight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fontSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>outlineSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowDepthX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowDepthY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分辨率语言方案序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分辨率方案序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏幕高度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>字体大小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轮廓大小</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴影横坐标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阴影纵坐标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>displayName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant displayName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant {75000be4}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant WEIGHT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant Style</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变体显示名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变体文件路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>字体显示名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变体权重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变体样式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>variant_index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变体序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PathHashToSelf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>italics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>underline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径检索字符串</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSS样式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加粗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>斜体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下划线</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰符标签</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>texture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纹理路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纵坐标偏移量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>localeType_index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言配置类型序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YAdjustment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -34569,6 +34859,357 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E52B18-32F2-44AB-BEB9-1A4D38FC3321}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3658</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3649</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3650</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3652</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3661</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3665</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3656</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3666</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3651</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3662</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3657</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3667</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3653</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3654</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3664</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
+    <sortCondition ref="A1:A13"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7F4C24-7612-49A7-BA2B-B3643B323BBD}">
   <sheetPr codeName="Sheet17"/>
@@ -35873,6 +36514,1401 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G86">
     <sortCondition ref="A1:A86"/>
   </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD168143-EF2F-4DA8-9552-0152D380A4CE}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3716</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3717</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3668</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3669</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3672</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3670</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3673</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0CB622-4366-4796-A425-D38A6B94B7C7}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3674</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3675</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3676</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3683</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3668</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>3677</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>3684</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>3678</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>3685</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>6</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>3679</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="15">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>3680</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>3687</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>8</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>3681</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>3682</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>3689</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B736A4E-0AE1-484F-B09E-E75E07B5469B}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3690</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3700</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3701</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3691</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3695</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3692</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3696</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3693</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3698</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>3694</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3699</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F8">
+    <sortCondition ref="A1:A8"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5E88C9-7DBC-4DF3-8CB1-5BAAF4537407}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3702</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="28">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>3703</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>3708</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3650</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3704</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3705</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3710</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>3706</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3711</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C075FD25-724E-4851-9475-612792A0E498}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3702</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="28">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>3703</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>3712</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3713</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3714</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3718</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3715</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B7" s="1"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="1"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8FF65B-8765-4B26-9217-24F2568E2396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15431AEF-FB2C-4BE8-96AA-B65691EDCEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="37" activeTab="43" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="20" activeTab="20" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -24483,6 +24483,9 @@
       <c r="E61" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
       <c r="G61">
         <v>241</v>
       </c>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15431AEF-FB2C-4BE8-96AA-B65691EDCEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F184FE-15D1-4BE5-9056-A590C0AA2938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="20" activeTab="20" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="10" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7340" uniqueCount="3719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7343" uniqueCount="3721">
   <si>
     <t>key</t>
   </si>
@@ -13365,6 +13365,14 @@
   </si>
   <si>
     <t>YAdjustment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>次级稀有度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不占用栏位</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -18774,7 +18782,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18794,7 +18802,7 @@
         <v>22</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18909,6 +18917,9 @@
       <c r="B17" s="1" t="s">
         <v>3571</v>
       </c>
+      <c r="C17" t="s">
+        <v>3719</v>
+      </c>
       <c r="D17" s="4" t="s">
         <v>3572</v>
       </c>
@@ -18916,7 +18927,7 @@
         <v>3572</v>
       </c>
       <c r="G17">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18933,7 +18944,7 @@
         <v>22</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -18963,6 +18974,9 @@
       <c r="B20" s="1" t="s">
         <v>3273</v>
       </c>
+      <c r="C20" t="s">
+        <v>3720</v>
+      </c>
       <c r="D20" s="4" t="s">
         <v>3572</v>
       </c>
@@ -18973,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -19368,7 +19382,7 @@
         <v>463</v>
       </c>
       <c r="G48">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -19419,7 +19433,7 @@
         <v>3572</v>
       </c>
       <c r="G51">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19850,7 +19864,7 @@
   <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="4"/>
@@ -20209,6 +20223,9 @@
       </c>
       <c r="B20" s="1" t="s">
         <v>3273</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3720</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>22</v>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F184FE-15D1-4BE5-9056-A590C0AA2938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC14397E-D99D-4E88-8D6C-68DF637D6444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="10" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -27,36 +27,37 @@
     <sheet name="SwarmAugment_header" sheetId="37" r:id="rId12"/>
     <sheet name="KiwiAugment_header" sheetId="6" r:id="rId13"/>
     <sheet name="KiwiAugmentSet_header" sheetId="35" r:id="rId14"/>
-    <sheet name="anvil_header" sheetId="11" r:id="rId15"/>
-    <sheet name="GoH_header" sheetId="40" r:id="rId16"/>
-    <sheet name="cameo_header" sheetId="44" r:id="rId17"/>
-    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId18"/>
-    <sheet name="CherryRound_header" sheetId="43" r:id="rId19"/>
-    <sheet name="CherryPhase_header" sheetId="42" r:id="rId20"/>
-    <sheet name="TFTSet_header" sheetId="15" r:id="rId21"/>
-    <sheet name="TFTShop_header" sheetId="17" r:id="rId22"/>
-    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId23"/>
-    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId24"/>
-    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId25"/>
-    <sheet name="TFTRound_header" sheetId="19" r:id="rId26"/>
-    <sheet name="TFTPortal_header" sheetId="27" r:id="rId27"/>
-    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId28"/>
-    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId29"/>
-    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId30"/>
-    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId31"/>
-    <sheet name="TFTItemList_header" sheetId="22" r:id="rId32"/>
-    <sheet name="TFTItem_header" sheetId="23" r:id="rId33"/>
-    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId34"/>
-    <sheet name="TFTTrait_header" sheetId="25" r:id="rId35"/>
-    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId36"/>
-    <sheet name="TFTScript_header" sheetId="26" r:id="rId37"/>
-    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId38"/>
-    <sheet name="fontDesc_header" sheetId="45" r:id="rId39"/>
-    <sheet name="fontType_header" sheetId="46" r:id="rId40"/>
-    <sheet name="fontResolution_header" sheetId="47" r:id="rId41"/>
-    <sheet name="fontStyle_header" sheetId="48" r:id="rId42"/>
-    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId43"/>
-    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId44"/>
+    <sheet name="augmentModifier_header" sheetId="53" r:id="rId15"/>
+    <sheet name="anvil_header" sheetId="11" r:id="rId16"/>
+    <sheet name="GoH_header" sheetId="40" r:id="rId17"/>
+    <sheet name="cameo_header" sheetId="44" r:id="rId18"/>
+    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId19"/>
+    <sheet name="CherryRound_header" sheetId="43" r:id="rId20"/>
+    <sheet name="CherryPhase_header" sheetId="42" r:id="rId21"/>
+    <sheet name="TFTSet_header" sheetId="15" r:id="rId22"/>
+    <sheet name="TFTShop_header" sheetId="17" r:id="rId23"/>
+    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId24"/>
+    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId25"/>
+    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId26"/>
+    <sheet name="TFTRound_header" sheetId="19" r:id="rId27"/>
+    <sheet name="TFTPortal_header" sheetId="27" r:id="rId28"/>
+    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId29"/>
+    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId30"/>
+    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId31"/>
+    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId32"/>
+    <sheet name="TFTItemList_header" sheetId="22" r:id="rId33"/>
+    <sheet name="TFTItem_header" sheetId="23" r:id="rId34"/>
+    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId35"/>
+    <sheet name="TFTTrait_header" sheetId="25" r:id="rId36"/>
+    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId37"/>
+    <sheet name="TFTScript_header" sheetId="26" r:id="rId38"/>
+    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId39"/>
+    <sheet name="fontDesc_header" sheetId="45" r:id="rId40"/>
+    <sheet name="fontType_header" sheetId="46" r:id="rId41"/>
+    <sheet name="fontResolution_header" sheetId="47" r:id="rId42"/>
+    <sheet name="fontStyle_header" sheetId="48" r:id="rId43"/>
+    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId44"/>
+    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId45"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$341</definedName>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7343" uniqueCount="3721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7400" uniqueCount="3749">
   <si>
     <t>key</t>
   </si>
@@ -13373,6 +13374,118 @@
   </si>
   <si>
     <t>不占用栏位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifierId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{30b1d74a}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ab0ba193}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{9346bce8}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{629a3429}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{6fd14d4c}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>修饰水印路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ab0ba193}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ab0ba193}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加文本键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{629a3429}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{629a3429}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加文本（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加文本（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{629a3429}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{629a3429}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加文本（中文/去格式化）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>附加文本（英文/去格式化）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属地图序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>belonging_mapId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ab0ba193}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ab0ba193}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头（中文/去格式化）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抬头（英文/去格式化）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -21299,6 +21412,327 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0948F58-759B-4003-B387-45192FD38987}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>3744</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3743</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3721</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3722</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3723</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3724</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3728</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3725</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3726</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3732</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3727</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3729</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3730</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3735</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3745</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3747</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3731</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3736</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>3746</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3748</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>3733</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3737</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>3739</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3741</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3734</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3738</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>3740</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3742</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F17">
+    <sortCondition ref="A1:A17"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457E3F81-9310-44BF-90A4-FF51EB2CBED2}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G28"/>
@@ -21813,7 +22247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF611F9-13A5-4CF6-B8E3-E0A2C9AC1592}">
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22280,7 +22714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656E066B-CAF0-4A5E-8BA4-5ACC1ECD3D32}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22547,7 +22981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8A9EE-70FA-478F-A3B9-CC27898022D4}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22712,149 +23146,6 @@
     </row>
     <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.2">
       <c r="B18" s="6"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D5B4D1-ED3B-471D-986E-326D93CEBEDE}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3607</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3608</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>3609</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3610</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>3611</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3612</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B6" s="1"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -23061,6 +23352,149 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D5B4D1-ED3B-471D-986E-326D93CEBEDE}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3607</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3608</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>3609</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3610</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>3611</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3612</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B6" s="1"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916B8D1A-71B4-46F4-B386-907D3EE40FC6}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -23362,7 +23796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3901968F-E5DF-4CBD-ADFB-08FA8A3F4044}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G299"/>
@@ -27648,7 +28082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40963FC-D1AF-47E5-BB09-9770285565C2}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G27"/>
@@ -28148,7 +28582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEED51C0-16CE-493B-ACDF-CED633B09365}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:G8"/>
@@ -28311,7 +28745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6ED802-F57E-44A6-B120-12D8C7BE7DFE}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G9"/>
@@ -28454,7 +28888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:G10"/>
@@ -28618,7 +29052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G68"/>
@@ -29975,7 +30409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B1F2EF-0DC6-4BB2-8172-4E4198527108}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:G28"/>
@@ -30466,7 +30900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:G10"/>
@@ -30649,331 +31083,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
-  <sheetPr codeName="Sheet28"/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="49.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2932</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2923</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2924</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2173</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2925</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2933</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2926</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2935</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2927</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2934</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2928</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2936</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>2929</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2930</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>2114</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2823</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2931</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2937</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>2938</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2940</v>
-      </c>
-      <c r="G15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>2939</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2941</v>
-      </c>
-      <c r="G16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2190</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2748</v>
-      </c>
-      <c r="G17">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
-    <sortCondition ref="A1:A17"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31896,6 +32005,331 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
+  <sheetPr codeName="Sheet28"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="49.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2924</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2933</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2927</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2934</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>2930</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2937</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2940</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>2939</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2941</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2748</v>
+      </c>
+      <c r="G17">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
+    <sortCondition ref="A1:A17"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G10"/>
@@ -32116,7 +32550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78003282-BF12-4B9E-88E0-0647BA982AE8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G29"/>
@@ -32594,7 +33028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8BF486-9605-4C14-9D33-B85EFC67F833}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G11"/>
@@ -32776,7 +33210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF0C918-C1C4-4CA0-AE17-312A0FD1DCCE}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:G51"/>
@@ -33733,7 +34167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC122C9-2D95-4069-BA3C-DDFB1C7F608D}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:G11"/>
@@ -33898,7 +34332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:G22"/>
@@ -34287,7 +34721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:G13"/>
@@ -34535,7 +34969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EAFC06-5BD2-40F9-AAC9-8F399DCA30B2}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:G10"/>
@@ -34676,7 +35110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:G10"/>
@@ -34873,357 +35307,6 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
     <sortCondition ref="A1:A10"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E52B18-32F2-44AB-BEB9-1A4D38FC3321}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2699</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2775</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3648</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3658</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3649</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3659</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3650</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3660</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3652</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3661</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3655</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3665</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3656</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3666</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3651</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3662</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3657</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3667</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>3653</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3663</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3654</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3664</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="1"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B18" s="6"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B19" s="6"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B20" s="6"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B21" s="6"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B22" s="6"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B23" s="6"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B24" s="6"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B25" s="6"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B26" s="6"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B27" s="6"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B28" s="6"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B29" s="6"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
-    <sortCondition ref="A1:A13"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36540,6 +36623,357 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E52B18-32F2-44AB-BEB9-1A4D38FC3321}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3648</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3658</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3649</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3650</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3652</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3661</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3655</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3665</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3656</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3666</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3651</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3662</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3657</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3667</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3653</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3654</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3664</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B23" s="6"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
+    <sortCondition ref="A1:A13"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD168143-EF2F-4DA8-9552-0152D380A4CE}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -36789,7 +37223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0CB622-4366-4796-A425-D38A6B94B7C7}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37115,7 +37549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B736A4E-0AE1-484F-B09E-E75E07B5469B}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37394,7 +37828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5E88C9-7DBC-4DF3-8CB1-5BAAF4537407}">
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37686,7 +38120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C075FD25-724E-4851-9475-612792A0E498}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC14397E-D99D-4E88-8D6C-68DF637D6444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCA8547-D876-42B3-9773-403BB44F856E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="10" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="12" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId45"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$345</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7400" uniqueCount="3749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7414" uniqueCount="3757">
   <si>
     <t>key</t>
   </si>
@@ -13486,6 +13486,38 @@
   </si>
   <si>
     <t>抬头（英文/去格式化）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mSpell mClientData mTooltipData mLocKeys keyKaynHackValue_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mSpell mClientData mTooltipData mLocKeys keyKaynHackValue_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯隐特有升级数值（中文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯隐特有升级数值（英文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mSpell mClientData mTooltipData mLocKeys keyKaynHackType_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mSpell mClientData mTooltipData mLocKeys keyKaynHackType_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯隐特有升级类型（中文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯隐特有升级类型（英文/数值转换）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -20306,6 +20338,9 @@
       <c r="D18" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E18" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G18">
         <v>9</v>
       </c>
@@ -20763,6 +20798,9 @@
       </c>
       <c r="C49" t="s">
         <v>463</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G49">
         <v>10</v>
@@ -46976,7 +47014,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE6CC07-A477-40B6-8242-7551C168A87A}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:G341"/>
+  <dimension ref="A1:G345"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="104.875" bestFit="1" customWidth="1"/>
@@ -47714,7 +47752,7 @@
         <v>22</v>
       </c>
       <c r="G39">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -47777,7 +47815,7 @@
         <v>22</v>
       </c>
       <c r="G42">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -47797,7 +47835,7 @@
         <v>22</v>
       </c>
       <c r="G43">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49727,7 +49765,7 @@
         <v>22</v>
       </c>
       <c r="G132">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49750,7 +49788,7 @@
         <v>0</v>
       </c>
       <c r="G133">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49773,7 +49811,7 @@
         <v>0</v>
       </c>
       <c r="G134">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49793,7 +49831,7 @@
         <v>0</v>
       </c>
       <c r="G135">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49816,7 +49854,7 @@
         <v>1</v>
       </c>
       <c r="G136">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49836,7 +49874,7 @@
         <v>22</v>
       </c>
       <c r="G137">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49856,7 +49894,7 @@
         <v>22</v>
       </c>
       <c r="G138">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49876,7 +49914,7 @@
         <v>22</v>
       </c>
       <c r="G139">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49896,7 +49934,7 @@
         <v>22</v>
       </c>
       <c r="G140">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49916,7 +49954,7 @@
         <v>22</v>
       </c>
       <c r="G141">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49939,7 +49977,7 @@
         <v>1</v>
       </c>
       <c r="G142">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49962,7 +50000,7 @@
         <v>0</v>
       </c>
       <c r="G143">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -49985,7 +50023,7 @@
         <v>0</v>
       </c>
       <c r="G144">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50005,7 +50043,7 @@
         <v>22</v>
       </c>
       <c r="G145">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50028,7 +50066,7 @@
         <v>1</v>
       </c>
       <c r="G146">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50048,7 +50086,7 @@
         <v>22</v>
       </c>
       <c r="G147">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50071,7 +50109,7 @@
         <v>0</v>
       </c>
       <c r="G148">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50088,7 +50126,7 @@
         <v>22</v>
       </c>
       <c r="G149">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50105,7 +50143,7 @@
         <v>22</v>
       </c>
       <c r="G150">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50122,7 +50160,7 @@
         <v>22</v>
       </c>
       <c r="G151">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50145,7 +50183,7 @@
         <v>1</v>
       </c>
       <c r="G152">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50165,7 +50203,7 @@
         <v>22</v>
       </c>
       <c r="G153">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50185,7 +50223,7 @@
         <v>22</v>
       </c>
       <c r="G154">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50205,7 +50243,7 @@
         <v>22</v>
       </c>
       <c r="G155">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50225,7 +50263,7 @@
         <v>22</v>
       </c>
       <c r="G156">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50245,7 +50283,7 @@
         <v>22</v>
       </c>
       <c r="G157">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50265,7 +50303,7 @@
         <v>22</v>
       </c>
       <c r="G158">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50285,7 +50323,7 @@
         <v>22</v>
       </c>
       <c r="G159">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50305,7 +50343,7 @@
         <v>22</v>
       </c>
       <c r="G160">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50325,7 +50363,7 @@
         <v>22</v>
       </c>
       <c r="G161">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50345,7 +50383,7 @@
         <v>22</v>
       </c>
       <c r="G162">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50368,7 +50406,7 @@
         <v>0</v>
       </c>
       <c r="G163">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50388,7 +50426,7 @@
         <v>22</v>
       </c>
       <c r="G164">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50411,7 +50449,7 @@
         <v>0</v>
       </c>
       <c r="G165">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50431,7 +50469,7 @@
         <v>22</v>
       </c>
       <c r="G166">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50448,7 +50486,7 @@
         <v>22</v>
       </c>
       <c r="G167">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50468,7 +50506,7 @@
         <v>22</v>
       </c>
       <c r="G168">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50491,7 +50529,7 @@
         <v>0</v>
       </c>
       <c r="G169">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50511,7 +50549,7 @@
         <v>22</v>
       </c>
       <c r="G170">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50531,7 +50569,7 @@
         <v>22</v>
       </c>
       <c r="G171">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50551,7 +50589,7 @@
         <v>22</v>
       </c>
       <c r="G172">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50574,7 +50612,7 @@
         <v>0</v>
       </c>
       <c r="G173">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50597,7 +50635,7 @@
         <v>0</v>
       </c>
       <c r="G174">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50617,7 +50655,7 @@
         <v>22</v>
       </c>
       <c r="G175">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50634,7 +50672,7 @@
         <v>22</v>
       </c>
       <c r="G176">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50654,7 +50692,7 @@
         <v>22</v>
       </c>
       <c r="G177">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50677,7 +50715,7 @@
         <v>0</v>
       </c>
       <c r="G178">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50700,7 +50738,7 @@
         <v>0</v>
       </c>
       <c r="G179">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50720,7 +50758,7 @@
         <v>22</v>
       </c>
       <c r="G180">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50743,7 +50781,7 @@
         <v>0</v>
       </c>
       <c r="G181">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50763,7 +50801,7 @@
         <v>22</v>
       </c>
       <c r="G182">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50786,7 +50824,7 @@
         <v>0</v>
       </c>
       <c r="G183">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50803,7 +50841,7 @@
         <v>22</v>
       </c>
       <c r="G184">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50823,7 +50861,7 @@
         <v>22</v>
       </c>
       <c r="G185">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50843,7 +50881,7 @@
         <v>22</v>
       </c>
       <c r="G186">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50863,7 +50901,7 @@
         <v>22</v>
       </c>
       <c r="G187">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50880,7 +50918,7 @@
         <v>22</v>
       </c>
       <c r="G188">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50900,7 +50938,7 @@
         <v>22</v>
       </c>
       <c r="G189">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50920,7 +50958,7 @@
         <v>22</v>
       </c>
       <c r="G190">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50940,7 +50978,7 @@
         <v>22</v>
       </c>
       <c r="G191">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50957,7 +50995,7 @@
         <v>22</v>
       </c>
       <c r="G192">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50977,7 +51015,7 @@
         <v>22</v>
       </c>
       <c r="G193">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50994,7 +51032,7 @@
         <v>22</v>
       </c>
       <c r="G194">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51011,7 +51049,7 @@
         <v>22</v>
       </c>
       <c r="G195">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51031,7 +51069,7 @@
         <v>22</v>
       </c>
       <c r="G196">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51051,7 +51089,7 @@
         <v>0</v>
       </c>
       <c r="G197">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51111,7 +51149,7 @@
         <v>22</v>
       </c>
       <c r="G200">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51131,7 +51169,7 @@
         <v>22</v>
       </c>
       <c r="G201">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51151,7 +51189,7 @@
         <v>22</v>
       </c>
       <c r="G202">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51171,7 +51209,7 @@
         <v>22</v>
       </c>
       <c r="G203">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51191,7 +51229,7 @@
         <v>22</v>
       </c>
       <c r="G204">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51211,7 +51249,7 @@
         <v>22</v>
       </c>
       <c r="G205">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51231,7 +51269,7 @@
         <v>22</v>
       </c>
       <c r="G206">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51291,7 +51329,7 @@
         <v>22</v>
       </c>
       <c r="G209">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51434,7 +51472,7 @@
         <v>0</v>
       </c>
       <c r="G216">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -51454,7 +51492,7 @@
         <v>22</v>
       </c>
       <c r="G217">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52074,7 +52112,7 @@
         <v>22</v>
       </c>
       <c r="G248">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52134,7 +52172,7 @@
         <v>22</v>
       </c>
       <c r="G251">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52154,7 +52192,7 @@
         <v>22</v>
       </c>
       <c r="G252">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52362,7 +52400,7 @@
         <v>22</v>
       </c>
       <c r="G263">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52370,16 +52408,16 @@
         <v>262</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>1442</v>
+        <v>3753</v>
       </c>
       <c r="C264" t="s">
-        <v>1527</v>
+        <v>3755</v>
       </c>
       <c r="E264" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G264">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52387,16 +52425,16 @@
         <v>263</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>1443</v>
+        <v>3754</v>
       </c>
       <c r="C265" t="s">
-        <v>1528</v>
+        <v>3756</v>
       </c>
       <c r="E265" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G265">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52404,16 +52442,16 @@
         <v>264</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>2084</v>
+        <v>1442</v>
       </c>
       <c r="C266" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G266">
-        <v>6</v>
+        <v>213</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52421,16 +52459,16 @@
         <v>265</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>2085</v>
+        <v>1443</v>
       </c>
       <c r="C267" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G267">
-        <v>7</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52438,10 +52476,10 @@
         <v>266</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>1444</v>
+        <v>3749</v>
       </c>
       <c r="C268" t="s">
-        <v>1531</v>
+        <v>3751</v>
       </c>
       <c r="E268" s="4" t="s">
         <v>22</v>
@@ -52455,10 +52493,10 @@
         <v>267</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>1445</v>
+        <v>3750</v>
       </c>
       <c r="C269" t="s">
-        <v>1532</v>
+        <v>3752</v>
       </c>
       <c r="E269" s="4" t="s">
         <v>22</v>
@@ -52472,16 +52510,16 @@
         <v>268</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>1446</v>
+        <v>2084</v>
       </c>
       <c r="C270" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="E270" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G270">
-        <v>215</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52489,16 +52527,16 @@
         <v>269</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>1447</v>
+        <v>2085</v>
       </c>
       <c r="C271" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="E271" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G271">
-        <v>217</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52506,16 +52544,16 @@
         <v>270</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="C272" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="E272" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G272">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52523,16 +52561,16 @@
         <v>271</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="C273" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="E273" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G273">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52540,16 +52578,16 @@
         <v>272</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="C274" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="E274" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G274">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52557,16 +52595,16 @@
         <v>273</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="C275" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="E275" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G275">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52574,16 +52612,16 @@
         <v>274</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="C276" t="s">
-        <v>1168</v>
+        <v>1535</v>
       </c>
       <c r="E276" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G276">
-        <v>185</v>
+        <v>223</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52591,16 +52629,16 @@
         <v>275</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="C277" t="s">
-        <v>1172</v>
+        <v>1536</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G277">
-        <v>186</v>
+        <v>225</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52608,16 +52646,16 @@
         <v>276</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="C278" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="E278" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G278">
-        <v>188</v>
+        <v>224</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52625,16 +52663,16 @@
         <v>277</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="C279" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G279">
-        <v>190</v>
+        <v>226</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52642,16 +52680,16 @@
         <v>278</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C280" t="s">
-        <v>1541</v>
+        <v>1168</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G280">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52659,16 +52697,16 @@
         <v>279</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C281" t="s">
-        <v>1542</v>
+        <v>1172</v>
       </c>
       <c r="E281" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G281">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52676,16 +52714,16 @@
         <v>280</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C282" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="E282" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G282">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52693,16 +52731,16 @@
         <v>281</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C283" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="E283" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G283">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52710,16 +52748,16 @@
         <v>282</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="C284" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="E284" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G284">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52727,16 +52765,16 @@
         <v>283</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C285" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="E285" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G285">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52744,16 +52782,16 @@
         <v>284</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="C286" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="E286" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G286">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52761,16 +52799,16 @@
         <v>285</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="C287" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="E287" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G287">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52778,16 +52816,16 @@
         <v>286</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="C288" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="E288" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G288">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52795,16 +52833,16 @@
         <v>287</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="C289" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="E289" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G289">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52812,16 +52850,16 @@
         <v>288</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="C290" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="E290" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G290">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52829,16 +52867,16 @@
         <v>289</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="C291" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="E291" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G291">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52846,16 +52884,16 @@
         <v>290</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="C292" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="E292" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G292">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52863,16 +52901,16 @@
         <v>291</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C293" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="E293" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G293">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52880,16 +52918,16 @@
         <v>292</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="C294" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="E294" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G294">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="295" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52897,16 +52935,16 @@
         <v>293</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="C295" t="s">
-        <v>1556</v>
+        <v>1552</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G295">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52914,16 +52952,16 @@
         <v>294</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="C296" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="E296" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G296">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52931,16 +52969,16 @@
         <v>295</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="C297" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="E297" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G297">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="298" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52948,16 +52986,16 @@
         <v>296</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="C298" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="E298" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G298">
-        <v>203</v>
+        <v>180</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52965,16 +53003,16 @@
         <v>297</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="C299" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="E299" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G299">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="300" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52982,16 +53020,16 @@
         <v>298</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="C300" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="E300" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G300">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="301" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -52999,90 +53037,84 @@
         <v>299</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="C301" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="E301" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G301">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="302" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>300</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>2042</v>
+      <c r="B302" s="6" t="s">
+        <v>1474</v>
       </c>
       <c r="C302" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>22</v>
+        <v>1559</v>
       </c>
       <c r="E302" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G302">
-        <v>165</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>301</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>2043</v>
+      <c r="B303" s="6" t="s">
+        <v>1475</v>
       </c>
       <c r="C303" t="s">
-        <v>2045</v>
-      </c>
-      <c r="D303" s="4" t="s">
-        <v>22</v>
+        <v>1560</v>
       </c>
       <c r="E303" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G303">
-        <v>166</v>
+        <v>205</v>
       </c>
     </row>
     <row r="304" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>302</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>2028</v>
-      </c>
-      <c r="D304" s="4" t="s">
-        <v>22</v>
+      <c r="B304" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1561</v>
       </c>
       <c r="E304" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G304">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="305" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>303</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>2047</v>
+      <c r="B305" s="6" t="s">
+        <v>1477</v>
       </c>
       <c r="C305" t="s">
-        <v>2048</v>
-      </c>
-      <c r="D305" s="4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E305" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G305">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="306" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53090,16 +53122,19 @@
         <v>304</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="C306" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E306" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G306">
-        <v>225</v>
+        <v>165</v>
       </c>
     </row>
     <row r="307" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53107,10 +53142,10 @@
         <v>305</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>2029</v>
+        <v>2043</v>
       </c>
       <c r="C307" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>22</v>
@@ -53119,7 +53154,7 @@
         <v>22</v>
       </c>
       <c r="G307">
-        <v>226</v>
+        <v>166</v>
       </c>
     </row>
     <row r="308" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53127,10 +53162,7 @@
         <v>306</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>2030</v>
-      </c>
-      <c r="C308" t="s">
-        <v>2051</v>
+        <v>2028</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>22</v>
@@ -53147,15 +53179,12 @@
         <v>307</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>2031</v>
+        <v>2047</v>
       </c>
       <c r="C309" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E309" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G309">
@@ -53167,15 +53196,12 @@
         <v>308</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>2032</v>
+        <v>2046</v>
       </c>
       <c r="C310" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E310" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G310">
@@ -53187,7 +53213,10 @@
         <v>309</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1728</v>
+        <v>2029</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2050</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>22</v>
@@ -53204,16 +53233,16 @@
         <v>310</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1729</v>
+        <v>2030</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2051</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E312" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F312" t="b">
-        <v>0</v>
       </c>
       <c r="G312">
         <v>231</v>
@@ -53224,16 +53253,19 @@
         <v>311</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1478</v>
+        <v>2031</v>
       </c>
       <c r="C313" t="s">
-        <v>1420</v>
+        <v>2052</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E313" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G313">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="314" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53241,16 +53273,19 @@
         <v>312</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1479</v>
+        <v>2032</v>
       </c>
       <c r="C314" t="s">
-        <v>1421</v>
+        <v>2053</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E314" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G314">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="315" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53258,10 +53293,7 @@
         <v>313</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C315" t="s">
-        <v>1563</v>
+        <v>1728</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>22</v>
@@ -53270,7 +53302,7 @@
         <v>22</v>
       </c>
       <c r="G315">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="316" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53278,16 +53310,19 @@
         <v>314</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C316" t="s">
-        <v>1564</v>
+        <v>1729</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E316" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F316" t="b">
+        <v>0</v>
+      </c>
       <c r="G316">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="317" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53295,16 +53330,16 @@
         <v>315</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="C317" t="s">
-        <v>1565</v>
+        <v>1420</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G317">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="318" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53312,10 +53347,10 @@
         <v>316</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="C318" t="s">
-        <v>1566</v>
+        <v>1421</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>22</v>
@@ -53329,10 +53364,10 @@
         <v>317</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="C319" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>22</v>
@@ -53341,7 +53376,7 @@
         <v>22</v>
       </c>
       <c r="G319">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="320" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53349,19 +53384,16 @@
         <v>318</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="C320" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E320" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G320">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="321" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53369,19 +53401,16 @@
         <v>319</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="C321" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E321" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G321">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="322" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53389,22 +53418,16 @@
         <v>320</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="C322" t="s">
-        <v>2062</v>
+        <v>1566</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E322" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F322" t="b">
-        <v>1</v>
-      </c>
       <c r="G322">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="323" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53412,10 +53435,10 @@
         <v>321</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="C323" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>22</v>
@@ -53423,11 +53446,8 @@
       <c r="E323" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F323" t="b">
-        <v>1</v>
-      </c>
       <c r="G323">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="324" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53435,10 +53455,10 @@
         <v>322</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C324" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>22</v>
@@ -53446,11 +53466,8 @@
       <c r="E324" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F324" t="b">
-        <v>1</v>
-      </c>
       <c r="G324">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="325" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53458,10 +53475,10 @@
         <v>323</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="C325" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>22</v>
@@ -53478,10 +53495,10 @@
         <v>324</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="C326" t="s">
-        <v>1573</v>
+        <v>2062</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>22</v>
@@ -53489,76 +53506,97 @@
       <c r="E326" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F326" t="b">
+        <v>1</v>
+      </c>
       <c r="G326">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="327" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>325</v>
       </c>
-      <c r="B327" s="6" t="s">
-        <v>1492</v>
+      <c r="B327" s="1" t="s">
+        <v>1488</v>
       </c>
       <c r="C327" t="s">
-        <v>1574</v>
+        <v>1570</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="E327" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F327" t="b">
+        <v>1</v>
+      </c>
       <c r="G327">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="328" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>326</v>
       </c>
-      <c r="B328" s="6" t="s">
-        <v>1493</v>
+      <c r="B328" s="1" t="s">
+        <v>1489</v>
       </c>
       <c r="C328" t="s">
-        <v>1575</v>
+        <v>1571</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="E328" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="F328" t="b">
+        <v>1</v>
+      </c>
       <c r="G328">
-        <v>247</v>
+        <v>266</v>
       </c>
     </row>
     <row r="329" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>327</v>
       </c>
-      <c r="B329" s="6" t="s">
-        <v>1494</v>
+      <c r="B329" s="1" t="s">
+        <v>1490</v>
       </c>
       <c r="C329" t="s">
-        <v>1576</v>
+        <v>1572</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G329">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="330" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>328</v>
       </c>
-      <c r="B330" s="6" t="s">
-        <v>1495</v>
+      <c r="B330" s="1" t="s">
+        <v>1491</v>
       </c>
       <c r="C330" t="s">
-        <v>1577</v>
+        <v>1573</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G330">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="331" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53566,13 +53604,16 @@
         <v>329</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="C331" t="s">
-        <v>1578</v>
+        <v>1574</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G331">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="332" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53580,13 +53621,16 @@
         <v>330</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="C332" t="s">
-        <v>1579</v>
+        <v>1575</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G332">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53594,10 +53638,10 @@
         <v>331</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="C333" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="E333" s="4" t="s">
         <v>22</v>
@@ -53611,10 +53655,10 @@
         <v>332</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="C334" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="E334" s="4" t="s">
         <v>22</v>
@@ -53628,16 +53672,13 @@
         <v>333</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="C335" t="s">
-        <v>1582</v>
-      </c>
-      <c r="E335" s="4" t="s">
-        <v>22</v>
+        <v>1578</v>
       </c>
       <c r="G335">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53645,16 +53686,13 @@
         <v>334</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="C336" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E336" s="4" t="s">
-        <v>22</v>
+        <v>1579</v>
       </c>
       <c r="G336">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53662,16 +53700,16 @@
         <v>335</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="C337" t="s">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="E337" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G337">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53679,16 +53717,16 @@
         <v>336</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="C338" t="s">
-        <v>1585</v>
+        <v>1581</v>
       </c>
       <c r="E338" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G338">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53696,16 +53734,16 @@
         <v>337</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="C339" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
       <c r="E339" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G339">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -53713,41 +53751,109 @@
         <v>338</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="C340" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="E340" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G340">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="341" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>339</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="B341" s="6" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C341" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G341">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C342" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G342">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C343" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E343" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G343">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C344" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G344">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C345" t="s">
         <v>1588</v>
       </c>
-      <c r="D341" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E341" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G341">
-        <v>339</v>
+      <c r="D345" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E345" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G345">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G341">
-    <sortCondition ref="A1:A341"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G345">
+    <sortCondition ref="A1:A345"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCA8547-D876-42B3-9773-403BB44F856E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DD499E-3EE2-463C-B67E-99CAE782A487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="12" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="2775" yWindow="2100" windowWidth="34725" windowHeight="18735" firstSheet="11" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -27,37 +27,38 @@
     <sheet name="SwarmAugment_header" sheetId="37" r:id="rId12"/>
     <sheet name="KiwiAugment_header" sheetId="6" r:id="rId13"/>
     <sheet name="KiwiAugmentSet_header" sheetId="35" r:id="rId14"/>
-    <sheet name="augmentModifier_header" sheetId="53" r:id="rId15"/>
-    <sheet name="anvil_header" sheetId="11" r:id="rId16"/>
-    <sheet name="GoH_header" sheetId="40" r:id="rId17"/>
-    <sheet name="cameo_header" sheetId="44" r:id="rId18"/>
-    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId19"/>
-    <sheet name="CherryRound_header" sheetId="43" r:id="rId20"/>
-    <sheet name="CherryPhase_header" sheetId="42" r:id="rId21"/>
-    <sheet name="TFTSet_header" sheetId="15" r:id="rId22"/>
-    <sheet name="TFTShop_header" sheetId="17" r:id="rId23"/>
-    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId24"/>
-    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId25"/>
-    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId26"/>
-    <sheet name="TFTRound_header" sheetId="19" r:id="rId27"/>
-    <sheet name="TFTPortal_header" sheetId="27" r:id="rId28"/>
-    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId29"/>
-    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId30"/>
-    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId31"/>
-    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId32"/>
-    <sheet name="TFTItemList_header" sheetId="22" r:id="rId33"/>
-    <sheet name="TFTItem_header" sheetId="23" r:id="rId34"/>
-    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId35"/>
-    <sheet name="TFTTrait_header" sheetId="25" r:id="rId36"/>
-    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId37"/>
-    <sheet name="TFTScript_header" sheetId="26" r:id="rId38"/>
-    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId39"/>
-    <sheet name="fontDesc_header" sheetId="45" r:id="rId40"/>
-    <sheet name="fontType_header" sheetId="46" r:id="rId41"/>
-    <sheet name="fontResolution_header" sheetId="47" r:id="rId42"/>
-    <sheet name="fontStyle_header" sheetId="48" r:id="rId43"/>
-    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId44"/>
-    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId45"/>
+    <sheet name="KiwiQuestline_header" sheetId="54" r:id="rId15"/>
+    <sheet name="augmentModifier_header" sheetId="53" r:id="rId16"/>
+    <sheet name="anvil_header" sheetId="11" r:id="rId17"/>
+    <sheet name="GoH_header" sheetId="40" r:id="rId18"/>
+    <sheet name="cameo_header" sheetId="44" r:id="rId19"/>
+    <sheet name="CherryRoundList_header" sheetId="41" r:id="rId20"/>
+    <sheet name="CherryRound_header" sheetId="43" r:id="rId21"/>
+    <sheet name="CherryPhase_header" sheetId="42" r:id="rId22"/>
+    <sheet name="TFTSet_header" sheetId="15" r:id="rId23"/>
+    <sheet name="TFTShop_header" sheetId="17" r:id="rId24"/>
+    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId25"/>
+    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId26"/>
+    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId27"/>
+    <sheet name="TFTRound_header" sheetId="19" r:id="rId28"/>
+    <sheet name="TFTPortal_header" sheetId="27" r:id="rId29"/>
+    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId30"/>
+    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId31"/>
+    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId32"/>
+    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId33"/>
+    <sheet name="TFTItemList_header" sheetId="22" r:id="rId34"/>
+    <sheet name="TFTItem_header" sheetId="23" r:id="rId35"/>
+    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId36"/>
+    <sheet name="TFTTrait_header" sheetId="25" r:id="rId37"/>
+    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId38"/>
+    <sheet name="TFTScript_header" sheetId="26" r:id="rId39"/>
+    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId40"/>
+    <sheet name="fontDesc_header" sheetId="45" r:id="rId41"/>
+    <sheet name="fontType_header" sheetId="46" r:id="rId42"/>
+    <sheet name="fontResolution_header" sheetId="47" r:id="rId43"/>
+    <sheet name="fontStyle_header" sheetId="48" r:id="rId44"/>
+    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId45"/>
+    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId46"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">champion_spell_header!$A$1:$G$345</definedName>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7414" uniqueCount="3757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7517" uniqueCount="3823">
   <si>
     <t>key</t>
   </si>
@@ -13518,6 +13519,259 @@
   </si>
   <si>
     <t>凯隐特有升级类型（英文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{e3a02eac}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{3ed971bd} {09d0cf3d}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线主键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能重载</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{bc1b3d88}</t>
+  </si>
+  <si>
+    <t>QuestName</t>
+  </si>
+  <si>
+    <t>{4796bf5f}</t>
+  </si>
+  <si>
+    <t>{c88f1a9b}</t>
+  </si>
+  <si>
+    <t>{ee2e0dbc}</t>
+  </si>
+  <si>
+    <t>{09d67381}</t>
+  </si>
+  <si>
+    <t>{06b06978} texturePath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {bc1b3d88}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline QuestName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {4796bf5f}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c88f1a9b}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {06b06978} texturePath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {ee2e0dbc}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline Milestones</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {09d67381}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线名称键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成描述键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务栏位图标纹理路径</t>
+  </si>
+  <si>
+    <t>任务栏位图标纹理路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相关强化符文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线代码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {4796bf5f}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {4796bf5f}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线对应强化符文名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线对应强化符文名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c88f1a9b}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c88f1a9b}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成描述（中文）</t>
+  </si>
+  <si>
+    <t>任务完成描述（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成描述（中文/数值转换）</t>
+  </si>
+  <si>
+    <t>任务完成描述（中文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c88f1a9b}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c88f1a9b}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成描述（英文）</t>
+  </si>
+  <si>
+    <t>任务完成描述（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务完成描述（英文/数值转换）</t>
+  </si>
+  <si>
+    <t>任务完成描述（英文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线里程信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone_index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {7fec0982}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {03d6a5a2}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{4796bf5f}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{4796bf5f}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务代码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线名称（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线名称（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {03d6a5a2}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {03d6a5a2}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程说明文本（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {03d6a5a2}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程说明文本（中文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milestone {03d6a5a2}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程说明文本（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程说明文本（英文/数值转换）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>里程说明文本键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{c88f1a9b}_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{c88f1a9b}_content_zh_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{c88f1a9b}_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{c88f1a9b}_content_en_burn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>augment AugmentPlatformId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -20006,11 +20260,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889E42AC-5584-44B0-BFBD-399F3EB60349}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="4"/>
   </cols>
@@ -20126,7 +20380,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20143,7 +20397,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20160,7 +20414,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20177,7 +20431,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20197,7 +20451,7 @@
         <v>22</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20217,7 +20471,7 @@
         <v>22</v>
       </c>
       <c r="G11">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20234,7 +20488,7 @@
         <v>22</v>
       </c>
       <c r="G12">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20254,7 +20508,7 @@
         <v>22</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20271,7 +20525,7 @@
         <v>22</v>
       </c>
       <c r="G14">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20288,7 +20542,7 @@
         <v>22</v>
       </c>
       <c r="G15">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20305,7 +20559,7 @@
         <v>22</v>
       </c>
       <c r="G16">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20322,7 +20576,7 @@
         <v>22</v>
       </c>
       <c r="G17">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20385,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20422,35 +20676,50 @@
         <v>3569</v>
       </c>
       <c r="G22">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>467</v>
+      <c r="B23" s="1" t="s">
+        <v>3758</v>
       </c>
       <c r="C23" t="s">
-        <v>474</v>
+        <v>3759</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>470</v>
+      <c r="B24" s="1" t="s">
+        <v>3757</v>
       </c>
       <c r="C24" t="s">
-        <v>475</v>
+        <v>3760</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20458,13 +20727,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C25" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G25">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20472,13 +20741,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C26" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="G26">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20486,13 +20755,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C27" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20500,13 +20769,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C28" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G28">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20514,13 +20783,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C29" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G29">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20528,13 +20797,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C30" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G30">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20542,13 +20811,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C31" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G31">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20556,13 +20825,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C32" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G32">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20570,13 +20839,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>3531</v>
+        <v>472</v>
       </c>
       <c r="C33" t="s">
-        <v>3547</v>
+        <v>473</v>
       </c>
       <c r="G33">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20584,13 +20853,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>3532</v>
+        <v>486</v>
       </c>
       <c r="C34" t="s">
-        <v>3548</v>
+        <v>488</v>
       </c>
       <c r="G34">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20598,13 +20867,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="C35" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="G35">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20612,13 +20881,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="C36" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="G36">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20626,13 +20895,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="C37" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
       <c r="G37">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20640,13 +20909,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="C38" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="G38">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20654,13 +20923,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="C39" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="G39">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20668,13 +20937,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="C40" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="G40">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20682,13 +20951,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="C41" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
       <c r="G41">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20696,13 +20965,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="C42" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="G42">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20710,13 +20979,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="C43" t="s">
-        <v>3557</v>
+        <v>3555</v>
       </c>
       <c r="G43">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20724,13 +20993,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="C44" t="s">
-        <v>3558</v>
+        <v>3556</v>
       </c>
       <c r="G44">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20738,13 +21007,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="C45" t="s">
-        <v>3559</v>
+        <v>3557</v>
       </c>
       <c r="G45">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20752,13 +21021,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="C46" t="s">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="G46">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20766,13 +21035,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="C47" t="s">
-        <v>3561</v>
+        <v>3559</v>
       </c>
       <c r="G47">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20780,13 +21049,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
       <c r="C48" t="s">
-        <v>3562</v>
+        <v>3560</v>
       </c>
       <c r="G48">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20794,16 +21063,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>462</v>
+        <v>3545</v>
       </c>
       <c r="C49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>22</v>
+        <v>3561</v>
       </c>
       <c r="G49">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20811,16 +21077,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>460</v>
+        <v>3546</v>
       </c>
       <c r="C50" t="s">
-        <v>461</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>22</v>
+        <v>3562</v>
       </c>
       <c r="G50">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20828,16 +21091,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="C51" t="s">
-        <v>480</v>
-      </c>
-      <c r="D51" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G51">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20845,16 +21108,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>3276</v>
+        <v>460</v>
       </c>
       <c r="C52" t="s">
-        <v>3277</v>
-      </c>
-      <c r="D52" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G52">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20862,13 +21125,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>3267</v>
+        <v>479</v>
       </c>
       <c r="C53" t="s">
-        <v>3266</v>
+        <v>480</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G53">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20876,13 +21142,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>3268</v>
+        <v>3276</v>
       </c>
       <c r="C54" t="s">
-        <v>3270</v>
+        <v>3277</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G54">
-        <v>12</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20890,35 +21159,267 @@
         <v>53</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
       <c r="C55" t="s">
-        <v>3271</v>
+        <v>3266</v>
       </c>
       <c r="G55">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="6" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3270</v>
+      </c>
+      <c r="G56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3271</v>
+      </c>
+      <c r="G57">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>3566</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C58" t="s">
         <v>3568</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>3569</v>
       </c>
-      <c r="G56">
-        <v>52</v>
+      <c r="G58">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>3768</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3781</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>3770</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>3771</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>3777</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>3772</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>3779</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>3773</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>3775</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>3780</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>65</v>
+      </c>
+      <c r="B67" s="56" t="s">
+        <v>3782</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>66</v>
+      </c>
+      <c r="B68" s="56" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>67</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>3786</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>3789</v>
+      </c>
+      <c r="G69">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>68</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>3791</v>
+      </c>
+      <c r="G70">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>69</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>3792</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>3795</v>
+      </c>
+      <c r="G71">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>70</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>3797</v>
+      </c>
+      <c r="G72">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G56">
-    <sortCondition ref="A1:A56"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G72">
+    <sortCondition ref="A1:A72"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21450,6 +21951,561 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD2F21B-D8AF-420D-A08D-54B532589448}">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3761</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3762</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3763</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3776</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3764</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3777</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3778</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3765</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3766</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3780</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3802</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3805</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3803</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3806</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3818</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3788</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>3819</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3790</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>3820</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3794</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>3799</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>3800</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>3810</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3801</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>3817</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>3807</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>3811</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>3812</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>3808</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3815</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>3814</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3816</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B24" s="6"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B25" s="6"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B26" s="6"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B27" s="6"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B29" s="6"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="6"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B31" s="6"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B32" s="6"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B33" s="6"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B34" s="6"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="6"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B36" s="6"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B37" s="6"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="6"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B39" s="1"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B40" s="6"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B41" s="6"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B42" s="6"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B43" s="6"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" s="6"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B45" s="6"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B46" s="6"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B47" s="6"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortCondition ref="A1:A23"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0948F58-759B-4003-B387-45192FD38987}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -21770,7 +22826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457E3F81-9310-44BF-90A4-FF51EB2CBED2}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G28"/>
@@ -22285,7 +23341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF611F9-13A5-4CF6-B8E3-E0A2C9AC1592}">
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -22752,7 +23808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656E066B-CAF0-4A5E-8BA4-5ACC1ECD3D32}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -23012,178 +24068,6 @@
       <c r="F16">
         <v>13</v>
       </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8A9EE-70FA-478F-A3B9-CC27898022D4}">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3575</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3580</v>
-      </c>
-      <c r="C3" t="s">
-        <v>630</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3576</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3578</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3577</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3579</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>3581</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>3583</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>3582</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>3584</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B8" s="1"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B16" s="6"/>
-    </row>
-    <row r="17" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="B18" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -23390,6 +24274,178 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8A9EE-70FA-478F-A3B9-CC27898022D4}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3575</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3580</v>
+      </c>
+      <c r="C3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3576</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3578</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3579</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3583</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>3582</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3584</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D5B4D1-ED3B-471D-986E-326D93CEBEDE}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -23532,7 +24588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916B8D1A-71B4-46F4-B386-907D3EE40FC6}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -23834,7 +24890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3901968F-E5DF-4CBD-ADFB-08FA8A3F4044}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G299"/>
@@ -28120,7 +29176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40963FC-D1AF-47E5-BB09-9770285565C2}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G27"/>
@@ -28620,7 +29676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEED51C0-16CE-493B-ACDF-CED633B09365}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:G8"/>
@@ -28783,7 +29839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6ED802-F57E-44A6-B120-12D8C7BE7DFE}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G9"/>
@@ -28926,7 +29982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:G10"/>
@@ -29090,7 +30146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G68"/>
@@ -30447,7 +31503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B1F2EF-0DC6-4BB2-8172-4E4198527108}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:G28"/>
@@ -30933,194 +31989,6 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G28">
     <sortCondition ref="A1:A28"/>
   </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
-  <sheetPr codeName="Sheet27"/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2775</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2916</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2917</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2918</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2919</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2920</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2921</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2922</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -32043,6 +32911,194 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
+  <sheetPr codeName="Sheet27"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2917</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2918</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2919</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2921</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2922</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:G17"/>
@@ -32367,7 +33423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G10"/>
@@ -32588,7 +33644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78003282-BF12-4B9E-88E0-0647BA982AE8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G29"/>
@@ -33066,7 +34122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8BF486-9605-4C14-9D33-B85EFC67F833}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G11"/>
@@ -33248,7 +34304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF0C918-C1C4-4CA0-AE17-312A0FD1DCCE}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:G51"/>
@@ -34205,7 +35261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC122C9-2D95-4069-BA3C-DDFB1C7F608D}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:G11"/>
@@ -34370,7 +35426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:G22"/>
@@ -34759,7 +35815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:G13"/>
@@ -35007,7 +36063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EAFC06-5BD2-40F9-AAC9-8F399DCA30B2}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:G10"/>
@@ -35143,209 +36199,6 @@
       <c r="B10" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
-  <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2565</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2283</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2622</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2284</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2623</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2287</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2624</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2625</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2626</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2290</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>2627</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2285</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>2628</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2286</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
-    <sortCondition ref="A1:A10"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36661,6 +37514,209 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
+  <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2285</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
+    <sortCondition ref="A1:A10"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E52B18-32F2-44AB-BEB9-1A4D38FC3321}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37011,7 +38067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD168143-EF2F-4DA8-9552-0152D380A4CE}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37261,7 +38317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0CB622-4366-4796-A425-D38A6B94B7C7}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37587,7 +38643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B736A4E-0AE1-484F-B09E-E75E07B5469B}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -37866,7 +38922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5E88C9-7DBC-4DF3-8CB1-5BAAF4537407}">
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -38158,7 +39214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C075FD25-724E-4851-9475-612792A0E498}">
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DD499E-3EE2-463C-B67E-99CAE782A487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA38324-AC6D-468F-82D3-EF20C3FA312D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="2100" windowWidth="34725" windowHeight="18735" firstSheet="11" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="12" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7517" uniqueCount="3823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7517" uniqueCount="3824">
   <si>
     <t>key</t>
   </si>
@@ -13772,6 +13772,10 @@
   </si>
   <si>
     <t>augment AugmentPlatformId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务线相关强化符文</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -20414,7 +20418,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20431,7 +20435,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20524,9 +20528,6 @@
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G14">
-        <v>46</v>
-      </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -20541,9 +20542,6 @@
       <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G15">
-        <v>51</v>
-      </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -20559,7 +20557,7 @@
         <v>22</v>
       </c>
       <c r="G16">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20576,7 +20574,7 @@
         <v>22</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20676,7 +20674,7 @@
         <v>3569</v>
       </c>
       <c r="G22">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20696,7 +20694,7 @@
         <v>22</v>
       </c>
       <c r="G23">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20984,9 +20982,6 @@
       <c r="C43" t="s">
         <v>3555</v>
       </c>
-      <c r="G43">
-        <v>47</v>
-      </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A44">
@@ -20998,9 +20993,6 @@
       <c r="C44" t="s">
         <v>3556</v>
       </c>
-      <c r="G44">
-        <v>48</v>
-      </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A45">
@@ -21012,9 +21004,6 @@
       <c r="C45" t="s">
         <v>3557</v>
       </c>
-      <c r="G45">
-        <v>49</v>
-      </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A46">
@@ -21026,9 +21015,6 @@
       <c r="C46" t="s">
         <v>3558</v>
       </c>
-      <c r="G46">
-        <v>50</v>
-      </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A47">
@@ -21040,9 +21026,6 @@
       <c r="C47" t="s">
         <v>3559</v>
       </c>
-      <c r="G47">
-        <v>52</v>
-      </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A48">
@@ -21054,9 +21037,6 @@
       <c r="C48" t="s">
         <v>3560</v>
       </c>
-      <c r="G48">
-        <v>53</v>
-      </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A49">
@@ -21068,9 +21048,6 @@
       <c r="C49" t="s">
         <v>3561</v>
       </c>
-      <c r="G49">
-        <v>54</v>
-      </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A50">
@@ -21082,9 +21059,6 @@
       <c r="C50" t="s">
         <v>3562</v>
       </c>
-      <c r="G50">
-        <v>55</v>
-      </c>
     </row>
     <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A51">
@@ -21134,7 +21108,7 @@
         <v>22</v>
       </c>
       <c r="G53">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21151,7 +21125,7 @@
         <v>22</v>
       </c>
       <c r="G54">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21210,7 +21184,7 @@
         <v>3569</v>
       </c>
       <c r="G58">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21287,7 +21261,7 @@
         <v>22</v>
       </c>
       <c r="G63">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21330,13 +21304,13 @@
         <v>3775</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>3780</v>
+        <v>3823</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G66">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA38324-AC6D-468F-82D3-EF20C3FA312D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C3F841-24D4-4859-8B30-123A84A23C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="12" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7517" uniqueCount="3824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7521" uniqueCount="3826">
   <si>
     <t>key</t>
   </si>
@@ -13776,6 +13776,14 @@
   </si>
   <si>
     <t>任务线相关强化符文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>questline {c504ece0}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{c504ece0}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -20264,7 +20272,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889E42AC-5584-44B0-BFBD-399F3EB60349}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
@@ -20384,7 +20392,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20401,7 +20409,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20418,7 +20426,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20435,7 +20443,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20492,7 +20500,7 @@
         <v>22</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20512,7 +20520,7 @@
         <v>22</v>
       </c>
       <c r="G13">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20557,7 +20565,7 @@
         <v>22</v>
       </c>
       <c r="G16">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20574,7 +20582,7 @@
         <v>22</v>
       </c>
       <c r="G17">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20674,7 +20682,7 @@
         <v>3569</v>
       </c>
       <c r="G22">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20694,7 +20702,7 @@
         <v>22</v>
       </c>
       <c r="G23">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20759,7 +20767,7 @@
         <v>476</v>
       </c>
       <c r="G27">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20773,7 +20781,7 @@
         <v>482</v>
       </c>
       <c r="G28">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20787,7 +20795,7 @@
         <v>477</v>
       </c>
       <c r="G29">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20801,7 +20809,7 @@
         <v>484</v>
       </c>
       <c r="G30">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20815,7 +20823,7 @@
         <v>478</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20829,7 +20837,7 @@
         <v>487</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20843,7 +20851,7 @@
         <v>473</v>
       </c>
       <c r="G33">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20857,7 +20865,7 @@
         <v>488</v>
       </c>
       <c r="G34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20871,7 +20879,7 @@
         <v>3547</v>
       </c>
       <c r="G35">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20885,7 +20893,7 @@
         <v>3548</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20899,7 +20907,7 @@
         <v>3549</v>
       </c>
       <c r="G37">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20913,7 +20921,7 @@
         <v>3550</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20927,7 +20935,7 @@
         <v>3551</v>
       </c>
       <c r="G39">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20941,7 +20949,7 @@
         <v>3552</v>
       </c>
       <c r="G40">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20955,7 +20963,7 @@
         <v>3553</v>
       </c>
       <c r="G41">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -20969,7 +20977,7 @@
         <v>3554</v>
       </c>
       <c r="G42">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21108,7 +21116,7 @@
         <v>22</v>
       </c>
       <c r="G53">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21125,7 +21133,7 @@
         <v>22</v>
       </c>
       <c r="G54">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21184,7 +21192,7 @@
         <v>3569</v>
       </c>
       <c r="G58">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21244,7 +21252,7 @@
         <v>22</v>
       </c>
       <c r="G62">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21261,7 +21269,7 @@
         <v>22</v>
       </c>
       <c r="G63">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21310,18 +21318,25 @@
         <v>22</v>
       </c>
       <c r="G66">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
-      <c r="B67" s="56" t="s">
-        <v>3782</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>3784</v>
+      <c r="B67" s="3" t="s">
+        <v>3824</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21329,10 +21344,10 @@
         <v>66</v>
       </c>
       <c r="B68" s="56" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21340,13 +21355,10 @@
         <v>67</v>
       </c>
       <c r="B69" s="56" t="s">
-        <v>3786</v>
+        <v>3783</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>3789</v>
-      </c>
-      <c r="G69">
-        <v>42</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -21354,10 +21366,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="G70">
         <v>43</v>
@@ -21368,10 +21380,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>3792</v>
+        <v>3787</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>3795</v>
+        <v>3791</v>
       </c>
       <c r="G71">
         <v>44</v>
@@ -21382,18 +21394,32 @@
         <v>70</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="G72">
         <v>45</v>
       </c>
     </row>
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>71</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>3797</v>
+      </c>
+      <c r="G73">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G72">
-    <sortCondition ref="A1:A72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G73">
+    <sortCondition ref="A1:A73"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21926,7 +21952,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD2F21B-D8AF-420D-A08D-54B532589448}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
@@ -22096,17 +22122,15 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>3802</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3805</v>
-      </c>
-      <c r="D10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>3825</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10">
-        <v>4</v>
+      <c r="F10" s="4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22114,16 +22138,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="C11" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22131,24 +22155,27 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3818</v>
+        <v>3803</v>
       </c>
       <c r="C12" t="s">
-        <v>3788</v>
+        <v>3806</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
+      <c r="G12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="C13" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -22159,10 +22186,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="C14" t="s">
-        <v>3794</v>
+        <v>3790</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -22173,43 +22200,38 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="C15" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="56" t="s">
-        <v>3799</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>3809</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B16" s="6" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16">
-        <v>6</v>
-      </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>3800</v>
+      <c r="B17" s="56" t="s">
+        <v>3799</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -22217,7 +22239,7 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22225,10 +22247,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>3817</v>
+        <v>3810</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
@@ -22236,24 +22258,26 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="56" t="s">
-        <v>3807</v>
+      <c r="B19" s="3" t="s">
+        <v>3801</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>3811</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>3817</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22261,16 +22285,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>3812</v>
+        <v>3807</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22278,16 +22302,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>3808</v>
+        <v>3812</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -22295,42 +22319,53 @@
         <v>20</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>3814</v>
+        <v>3808</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+      <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>3822</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B23" s="56" t="s">
+        <v>3814</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3816</v>
+      </c>
+      <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B24" s="6"/>
-      <c r="D24" s="4"/>
+      <c r="A24" s="7">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
+      <c r="G24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
@@ -22417,13 +22452,13 @@
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B39" s="1"/>
+      <c r="B39" s="6"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B40" s="6"/>
+      <c r="B40" s="1"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -22470,9 +22505,15 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
+    <row r="48" spans="2:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="B48" s="6"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
-    <sortCondition ref="A1:A23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G24">
+    <sortCondition ref="A1:A24"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C682FE-77D1-4962-B8FA-B14A4FD5AB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36FC1F-4A21-4A6B-B1BF-4CB3FF3E79C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="8" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -40776,7 +40776,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -40793,7 +40793,7 @@
         <v>22</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -40813,7 +40813,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -46103,7 +46103,7 @@
         <v>22</v>
       </c>
       <c r="G263">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -46510,7 +46510,7 @@
         <v>22</v>
       </c>
       <c r="G285">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -46527,7 +46527,7 @@
         <v>22</v>
       </c>
       <c r="G286">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50434,6 +50434,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC956E1D-A581-434A-AB3C-C56FE7FC755F}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G373"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -50544,7 +50545,7 @@
         <v/>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50571,7 +50572,7 @@
         <v/>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -50598,7 +50599,7 @@
         <v/>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70436,6 +70437,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D84A2DE-E2C4-418D-B1B3-5725D9F0E6FA}">
+  <sheetPr codeName="Sheet48"/>
   <dimension ref="A1:G383"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -70479,7 +70481,7 @@
         <v>2073</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70493,7 +70495,7 @@
         <v>2053</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70510,7 +70512,7 @@
         <v>22</v>
       </c>
       <c r="G4">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70527,7 +70529,7 @@
         <v>22</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70544,7 +70546,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70564,7 +70566,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70578,7 +70580,7 @@
         <v>2063</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70595,7 +70597,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70612,7 +70614,7 @@
         <v>22</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70626,7 +70628,7 @@
         <v>2074</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70707,7 +70709,7 @@
         <v/>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70734,7 +70736,7 @@
         <v/>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -70761,7 +70763,7 @@
         <v/>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -77700,7 +77702,7 @@
         <v/>
       </c>
       <c r="G273">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -78294,7 +78296,7 @@
         <v/>
       </c>
       <c r="G295">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -78321,7 +78323,7 @@
         <v/>
       </c>
       <c r="G296">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="15" x14ac:dyDescent="0.2">

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36FC1F-4A21-4A6B-B1BF-4CB3FF3E79C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324CE537-6F40-4A4D-AF72-7EA852D0F5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="8" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8411" uniqueCount="3895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8415" uniqueCount="3899">
   <si>
     <t>key</t>
   </si>
@@ -14071,6 +14071,22 @@
   </si>
   <si>
     <t>rootAbility_AbilityTraits</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在于当前版本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在于怀旧版本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>isCurrent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>isClassic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25128,7 +25144,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889E42AC-5584-44B0-BFBD-399F3EB60349}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
@@ -25164,34 +25180,28 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="6" t="s">
+        <v>3897</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>3895</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>437</v>
+      <c r="B3" s="6" t="s">
+        <v>3898</v>
       </c>
       <c r="C3" t="s">
-        <v>438</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
+        <v>3896</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25199,22 +25209,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>448</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="G4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25222,16 +25226,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25239,16 +25243,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C6" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G6">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25256,16 +25266,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25273,16 +25283,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25290,16 +25300,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3266</v>
+        <v>441</v>
       </c>
       <c r="C9" t="s">
-        <v>3267</v>
+        <v>444</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G9">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25307,19 +25317,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C10" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G10">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25327,19 +25334,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>451</v>
+        <v>3266</v>
       </c>
       <c r="C11" t="s">
-        <v>452</v>
+        <v>3267</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G11">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25347,16 +25351,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3515</v>
+        <v>449</v>
       </c>
       <c r="C12" t="s">
-        <v>3519</v>
+        <v>450</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G12">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25364,10 +25371,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3516</v>
+        <v>451</v>
       </c>
       <c r="C13" t="s">
-        <v>3520</v>
+        <v>452</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -25376,7 +25383,7 @@
         <v>22</v>
       </c>
       <c r="G13">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25384,13 +25391,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="C14" t="s">
-        <v>3522</v>
+        <v>3519</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="G14">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25398,13 +25408,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="C15" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25412,16 +25428,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>465</v>
+        <v>3517</v>
       </c>
       <c r="C16" t="s">
-        <v>466</v>
+        <v>3522</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="G16">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25429,16 +25442,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>453</v>
+        <v>3518</v>
       </c>
       <c r="C17" t="s">
-        <v>454</v>
+        <v>3521</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="G17">
-        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25446,19 +25456,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="C18" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G18">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25466,19 +25473,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C19" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G19">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25486,10 +25490,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3265</v>
+        <v>455</v>
       </c>
       <c r="C20" t="s">
-        <v>3712</v>
+        <v>456</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>22</v>
@@ -25497,11 +25501,8 @@
       <c r="E20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="G20">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25509,16 +25510,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C21" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E21" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G21">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25526,19 +25530,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3557</v>
+        <v>3265</v>
       </c>
       <c r="C22" t="s">
-        <v>3559</v>
+        <v>3712</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>3561</v>
+        <v>22</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3561</v>
+        <v>22</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25546,19 +25553,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3750</v>
+        <v>459</v>
       </c>
       <c r="C23" t="s">
-        <v>3751</v>
+        <v>464</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G23">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25566,50 +25570,62 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3749</v>
+        <v>3557</v>
       </c>
       <c r="C24" t="s">
-        <v>3752</v>
+        <v>3559</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>22</v>
+        <v>3561</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="4" t="b">
-        <v>0</v>
+        <v>3561</v>
       </c>
       <c r="G24">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>467</v>
+      <c r="B25" s="1" t="s">
+        <v>3750</v>
       </c>
       <c r="C25" t="s">
-        <v>474</v>
+        <v>3751</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>470</v>
+      <c r="B26" s="1" t="s">
+        <v>3749</v>
       </c>
       <c r="C26" t="s">
-        <v>475</v>
+        <v>3752</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25617,13 +25633,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C27" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G27">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25631,13 +25647,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C28" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="G28">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25645,10 +25661,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G29">
         <v>25</v>
@@ -25659,10 +25675,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C30" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G30">
         <v>26</v>
@@ -25673,13 +25689,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25687,13 +25703,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C32" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G32">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25701,10 +25717,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C33" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G33">
         <v>30</v>
@@ -25715,10 +25731,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C34" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G34">
         <v>31</v>
@@ -25729,13 +25745,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>3523</v>
+        <v>472</v>
       </c>
       <c r="C35" t="s">
-        <v>3539</v>
+        <v>473</v>
       </c>
       <c r="G35">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25743,13 +25759,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>3524</v>
+        <v>486</v>
       </c>
       <c r="C36" t="s">
-        <v>3540</v>
+        <v>488</v>
       </c>
       <c r="G36">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25757,10 +25773,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>3525</v>
+        <v>3523</v>
       </c>
       <c r="C37" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="G37">
         <v>35</v>
@@ -25771,10 +25787,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="C38" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="G38">
         <v>36</v>
@@ -25785,13 +25801,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="C39" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="G39">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25799,13 +25815,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="C40" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="G40">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25813,10 +25829,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>3529</v>
+        <v>3527</v>
       </c>
       <c r="C41" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="G41">
         <v>40</v>
@@ -25827,10 +25843,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
       <c r="C42" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
       <c r="G42">
         <v>41</v>
@@ -25841,10 +25857,13 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
       <c r="C43" t="s">
-        <v>3547</v>
+        <v>3545</v>
+      </c>
+      <c r="G43">
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25852,10 +25871,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="C44" t="s">
-        <v>3548</v>
+        <v>3546</v>
+      </c>
+      <c r="G44">
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25863,10 +25885,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="C45" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25874,10 +25896,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="C46" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25885,10 +25907,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="C47" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25896,10 +25918,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="C48" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25907,10 +25929,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="C49" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25918,10 +25940,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="C50" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25929,16 +25951,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>462</v>
+        <v>3537</v>
       </c>
       <c r="C51" t="s">
-        <v>463</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51">
-        <v>10</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25946,16 +25962,10 @@
         <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>460</v>
+        <v>3538</v>
       </c>
       <c r="C52" t="s">
-        <v>461</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52">
-        <v>8</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25963,16 +25973,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="C53" t="s">
-        <v>480</v>
-      </c>
-      <c r="D53" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G53">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25980,16 +25990,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>3268</v>
+        <v>460</v>
       </c>
       <c r="C54" t="s">
-        <v>3269</v>
-      </c>
-      <c r="D54" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G54">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -25997,13 +26007,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>3259</v>
+        <v>479</v>
       </c>
       <c r="C55" t="s">
-        <v>3258</v>
+        <v>480</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G55">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26011,13 +26024,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>3260</v>
+        <v>3268</v>
       </c>
       <c r="C56" t="s">
-        <v>3262</v>
+        <v>3269</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G56">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26025,10 +26041,10 @@
         <v>55</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
       <c r="C57" t="s">
-        <v>3263</v>
+        <v>3258</v>
       </c>
       <c r="G57">
         <v>13</v>
@@ -26038,49 +26054,45 @@
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="6" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3262</v>
+      </c>
+      <c r="G58">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3263</v>
+      </c>
+      <c r="G59">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>3558</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>3560</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>3561</v>
       </c>
-      <c r="G58">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A59" s="2">
-        <v>57</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>3760</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>58</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>3761</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>3773</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G60">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26088,10 +26100,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>3762</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>3768</v>
+        <v>3760</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61">
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26099,16 +26115,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G62">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26116,16 +26132,10 @@
         <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>3771</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63">
-        <v>57</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26133,20 +26143,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>3765</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>3763</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>3769</v>
+      </c>
       <c r="D64" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F64" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="G64">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26154,10 +26160,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>3790</v>
+        <v>3771</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65">
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26165,16 +26177,20 @@
         <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>3767</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>3815</v>
-      </c>
+        <v>3765</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E66" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="G66">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26182,39 +26198,45 @@
         <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>3816</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>21</v>
+        <v>3766</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>3790</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
-      <c r="B68" s="56" t="s">
-        <v>3774</v>
+      <c r="B68" s="3" t="s">
+        <v>3767</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>3776</v>
+        <v>3815</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68">
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
-      <c r="B69" s="56" t="s">
-        <v>3775</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>3777</v>
+      <c r="B69" s="3" t="s">
+        <v>3816</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26222,13 +26244,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>3778</v>
+        <v>3774</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>3781</v>
-      </c>
-      <c r="G70">
-        <v>43</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26236,13 +26255,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>3779</v>
+        <v>3775</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>3783</v>
-      </c>
-      <c r="G71">
-        <v>44</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26250,10 +26266,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>3784</v>
+        <v>3778</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>3787</v>
+        <v>3781</v>
       </c>
       <c r="G72">
         <v>45</v>
@@ -26264,18 +26280,46 @@
         <v>71</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>3785</v>
+        <v>3779</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>3789</v>
+        <v>3783</v>
       </c>
       <c r="G73">
         <v>46</v>
       </c>
     </row>
+    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>72</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>3784</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>3787</v>
+      </c>
+      <c r="G74">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>73</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>3785</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>3789</v>
+      </c>
+      <c r="G75">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G73">
-    <sortCondition ref="A1:A73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G75">
+    <sortCondition ref="A1:A75"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324CE537-6F40-4A4D-AF72-7EA852D0F5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44ACB5D0-A245-4C95-A6C6-4AA7EC9426D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="14" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="6" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8415" uniqueCount="3899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8423" uniqueCount="3907">
   <si>
     <t>key</t>
   </si>
@@ -14087,6 +14087,38 @@
   </si>
   <si>
     <t>isClassic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>belonging_perkstyle_key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>belonging_perkstyle mDisplayNameLocalizationKey_content_zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>belonging_perkstyle mDisplayNameLocalizationKey_content_en</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属符文系主键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属符文系显示名（中文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属符文系显示名（英文）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>belonging_perkstyle_slotIndex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属符文系槽位序号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -61877,10 +61909,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7D9E21-BBB5-4A35-B254-A9AA06BCF8B0}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="4"/>
@@ -61994,7 +62026,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62014,7 +62046,7 @@
         <v>22</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62034,7 +62066,7 @@
         <v>22</v>
       </c>
       <c r="G8">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62054,7 +62086,7 @@
         <v>22</v>
       </c>
       <c r="G9">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62074,7 +62106,7 @@
         <v>22</v>
       </c>
       <c r="G10">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62094,7 +62126,7 @@
         <v>22</v>
       </c>
       <c r="G11">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62111,7 +62143,7 @@
         <v>22</v>
       </c>
       <c r="G12">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62134,7 +62166,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62157,7 +62189,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62174,7 +62206,7 @@
         <v>22</v>
       </c>
       <c r="G15">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62188,7 +62220,7 @@
         <v>2165</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62208,7 +62240,7 @@
         <v>22</v>
       </c>
       <c r="G17">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62228,7 +62260,7 @@
         <v>22</v>
       </c>
       <c r="G18">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62248,7 +62280,7 @@
         <v>22</v>
       </c>
       <c r="G19">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62271,7 +62303,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62291,7 +62323,7 @@
         <v>22</v>
       </c>
       <c r="G21">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62311,7 +62343,7 @@
         <v>22</v>
       </c>
       <c r="G22">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62353,7 +62385,7 @@
         <v>476</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62367,7 +62399,7 @@
         <v>477</v>
       </c>
       <c r="G26">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62381,7 +62413,7 @@
         <v>482</v>
       </c>
       <c r="G27">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62395,7 +62427,7 @@
         <v>484</v>
       </c>
       <c r="G28">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62409,7 +62441,7 @@
         <v>3161</v>
       </c>
       <c r="G29">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62423,7 +62455,7 @@
         <v>3162</v>
       </c>
       <c r="G30">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62437,7 +62469,7 @@
         <v>2900</v>
       </c>
       <c r="G31">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62451,7 +62483,7 @@
         <v>2901</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62465,7 +62497,7 @@
         <v>2902</v>
       </c>
       <c r="G33">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62479,7 +62511,7 @@
         <v>2903</v>
       </c>
       <c r="G34">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62493,7 +62525,7 @@
         <v>1312</v>
       </c>
       <c r="G35">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62507,7 +62539,7 @@
         <v>1313</v>
       </c>
       <c r="G36">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62521,7 +62553,7 @@
         <v>3213</v>
       </c>
       <c r="G37">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62535,7 +62567,7 @@
         <v>3214</v>
       </c>
       <c r="G38">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62549,7 +62581,7 @@
         <v>3168</v>
       </c>
       <c r="G39">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62563,12 +62595,65 @@
         <v>3169</v>
       </c>
       <c r="G40">
-        <v>30</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3899</v>
+      </c>
+      <c r="C41" t="s">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3900</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3903</v>
+      </c>
+      <c r="G42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3901</v>
+      </c>
+      <c r="C43" t="s">
+        <v>3904</v>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3905</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3906</v>
+      </c>
+      <c r="G44">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G40">
-    <sortCondition ref="A1:A40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G44">
+    <sortCondition ref="A1:A44"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Game Data Extraction Main Dataframe Structure.xlsx
+++ b/Game Data Extraction Main Dataframe Structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F170A0-4AFE-4E08-89C5-756DA6F64A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7726EA-2CAE-4D1B-A8C0-A2DBC7252110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="7" activeTab="8" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="17" activeTab="24" xr2:uid="{3B9B600D-37BF-42AF-A848-4C9EEE49C701}"/>
   </bookViews>
   <sheets>
     <sheet name="gameModeMap_header" sheetId="4" r:id="rId1"/>
@@ -37,30 +37,31 @@
     <sheet name="CherryRoundList_header" sheetId="41" r:id="rId22"/>
     <sheet name="CherryRound_header" sheetId="43" r:id="rId23"/>
     <sheet name="CherryPhase_header" sheetId="42" r:id="rId24"/>
-    <sheet name="TFTSet_header" sheetId="15" r:id="rId25"/>
-    <sheet name="TFTShop_header" sheetId="17" r:id="rId26"/>
-    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId27"/>
-    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId28"/>
-    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId29"/>
-    <sheet name="TFTRound_header" sheetId="19" r:id="rId30"/>
-    <sheet name="TFTPortal_header" sheetId="27" r:id="rId31"/>
-    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId32"/>
-    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId33"/>
-    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId34"/>
-    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId35"/>
-    <sheet name="TFTItemList_header" sheetId="22" r:id="rId36"/>
-    <sheet name="TFTItem_header" sheetId="23" r:id="rId37"/>
-    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId38"/>
-    <sheet name="TFTTrait_header" sheetId="25" r:id="rId39"/>
-    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId40"/>
-    <sheet name="TFTScript_header" sheetId="26" r:id="rId41"/>
-    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId42"/>
-    <sheet name="fontDesc_header" sheetId="45" r:id="rId43"/>
-    <sheet name="fontType_header" sheetId="46" r:id="rId44"/>
-    <sheet name="fontResolution_header" sheetId="47" r:id="rId45"/>
-    <sheet name="fontStyle_header" sheetId="48" r:id="rId46"/>
-    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId47"/>
-    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId48"/>
+    <sheet name="CherryRoundPhase_header" sheetId="58" r:id="rId25"/>
+    <sheet name="TFTSet_header" sheetId="15" r:id="rId26"/>
+    <sheet name="TFTShop_header" sheetId="17" r:id="rId27"/>
+    <sheet name="TFTShopContent_header" sheetId="31" r:id="rId28"/>
+    <sheet name="TFTDropRate_header" sheetId="18" r:id="rId29"/>
+    <sheet name="TFTStageRound_header" sheetId="32" r:id="rId30"/>
+    <sheet name="TFTRound_header" sheetId="19" r:id="rId31"/>
+    <sheet name="TFTPortal_header" sheetId="27" r:id="rId32"/>
+    <sheet name="TFTEncounterDistribution_header" sheetId="28" r:id="rId33"/>
+    <sheet name="TFTEncounter_header" sheetId="29" r:id="rId34"/>
+    <sheet name="TFTUnitProperty_header" sheetId="16" r:id="rId35"/>
+    <sheet name="TFTCharacterRole_header" sheetId="21" r:id="rId36"/>
+    <sheet name="TFTItemList_header" sheetId="22" r:id="rId37"/>
+    <sheet name="TFTItem_header" sheetId="23" r:id="rId38"/>
+    <sheet name="TFTTraitList_header" sheetId="24" r:id="rId39"/>
+    <sheet name="TFTTrait_header" sheetId="25" r:id="rId40"/>
+    <sheet name="TFTPVENPC_header" sheetId="30" r:id="rId41"/>
+    <sheet name="TFTScript_header" sheetId="26" r:id="rId42"/>
+    <sheet name="TFTAnnouncement_header" sheetId="20" r:id="rId43"/>
+    <sheet name="fontDesc_header" sheetId="45" r:id="rId44"/>
+    <sheet name="fontType_header" sheetId="46" r:id="rId45"/>
+    <sheet name="fontResolution_header" sheetId="47" r:id="rId46"/>
+    <sheet name="fontStyle_header" sheetId="48" r:id="rId47"/>
+    <sheet name="font_CSSStyle_header" sheetId="50" r:id="rId48"/>
+    <sheet name="font_CSSIcon_header" sheetId="51" r:id="rId49"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">champion_spell_header!$A$1:$G$343</definedName>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8417" uniqueCount="3902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8467" uniqueCount="3922">
   <si>
     <t>key</t>
   </si>
@@ -12829,54 +12830,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>phase number</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phase type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phase duration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phase FlashOnTimeRemaining</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phase SecondFlashOnTimeRemaining</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phase TimerBarDefaultColor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>即将到来的事件缩略图路径</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>正在发生的事件缩略图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>已经完成的事件缩略图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶段类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>回合类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>阶段持续时间（秒）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>第一次闪烁倒计时</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -14099,6 +14060,111 @@
   </si>
   <si>
     <t>所属符文系槽位序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PhaseNumber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PhaseKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DisplayNameTra_content_zh</t>
+  </si>
+  <si>
+    <t>DisplayNameTra_content_en</t>
+  </si>
+  <si>
+    <t>阶段数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段主键</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示名键</t>
+  </si>
+  <si>
+    <t>即将到来的事件缩略图路径</t>
+  </si>
+  <si>
+    <t>显示名（中文）</t>
+  </si>
+  <si>
+    <t>显示名（英文）</t>
+  </si>
+  <si>
+    <t>第一次闪烁倒计时</t>
+  </si>
+  <si>
+    <t>第二次闪烁倒计时</t>
+  </si>
+  <si>
+    <t>时间轴默认颜色方案</t>
+  </si>
+  <si>
+    <t>subPhase number</t>
+  </si>
+  <si>
+    <t>subPhase type</t>
+  </si>
+  <si>
+    <t>subPhase duration</t>
+  </si>
+  <si>
+    <t>subPhase FlashOnTimeRemaining</t>
+  </si>
+  <si>
+    <t>subPhase SecondFlashOnTimeRemaining</t>
+  </si>
+  <si>
+    <t>subPhase TimerBarDefaultColor</t>
+  </si>
+  <si>
+    <t>subPhase number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>subPhase type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>subPhase duration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>subPhase FlashOnTimeRemaining</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>subPhase SecondFlashOnTimeRemaining</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>subPhase TimerBarDefaultColor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在发生的事件缩略图路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经完成的事件缩略图路径</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子阶段序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子阶段类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子阶段持续时间（秒）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24213,7 +24279,7 @@
         <v>3560</v>
       </c>
       <c r="C17" t="s">
-        <v>3708</v>
+        <v>3698</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>3561</v>
@@ -24270,7 +24336,7 @@
         <v>3262</v>
       </c>
       <c r="C20" t="s">
-        <v>3709</v>
+        <v>3699</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>3561</v>
@@ -25193,10 +25259,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>3892</v>
+        <v>3882</v>
       </c>
       <c r="C2" t="s">
-        <v>3890</v>
+        <v>3880</v>
       </c>
       <c r="G2">
         <v>7</v>
@@ -25207,10 +25273,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>3893</v>
+        <v>3883</v>
       </c>
       <c r="C3" t="s">
-        <v>3891</v>
+        <v>3881</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -25545,7 +25611,7 @@
         <v>3262</v>
       </c>
       <c r="C22" t="s">
-        <v>3709</v>
+        <v>3699</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>22</v>
@@ -25602,10 +25668,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3747</v>
+        <v>3737</v>
       </c>
       <c r="C25" t="s">
-        <v>3748</v>
+        <v>3738</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>22</v>
@@ -25622,10 +25688,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3746</v>
+        <v>3736</v>
       </c>
       <c r="C26" t="s">
-        <v>3749</v>
+        <v>3739</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>22</v>
@@ -26112,7 +26178,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>3757</v>
+        <v>3747</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="4" t="s">
@@ -26127,10 +26193,10 @@
         <v>60</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>3758</v>
+        <v>3748</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>3770</v>
+        <v>3760</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>22</v>
@@ -26144,10 +26210,10 @@
         <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>3759</v>
+        <v>3749</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>3765</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26155,10 +26221,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>3760</v>
+        <v>3750</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>3766</v>
+        <v>3756</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>22</v>
@@ -26172,10 +26238,10 @@
         <v>63</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>3761</v>
+        <v>3751</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>3768</v>
+        <v>3758</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>22</v>
@@ -26189,7 +26255,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>3762</v>
+        <v>3752</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="4" t="s">
@@ -26210,10 +26276,10 @@
         <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>3763</v>
+        <v>3753</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>3787</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26221,10 +26287,10 @@
         <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>3764</v>
+        <v>3754</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>3812</v>
+        <v>3802</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>22</v>
@@ -26238,7 +26304,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>3813</v>
+        <v>3803</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="4" t="s">
@@ -26256,10 +26322,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>3771</v>
+        <v>3761</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>3773</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26267,10 +26333,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="56" t="s">
-        <v>3772</v>
+        <v>3762</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>3774</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -26278,10 +26344,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>3775</v>
+        <v>3765</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>3778</v>
+        <v>3768</v>
       </c>
       <c r="G72">
         <v>45</v>
@@ -26292,10 +26358,10 @@
         <v>71</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>3776</v>
+        <v>3766</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>3780</v>
+        <v>3770</v>
       </c>
       <c r="G73">
         <v>46</v>
@@ -26306,10 +26372,10 @@
         <v>72</v>
       </c>
       <c r="B74" s="56" t="s">
-        <v>3781</v>
+        <v>3771</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>3784</v>
+        <v>3774</v>
       </c>
       <c r="G74">
         <v>47</v>
@@ -26320,10 +26386,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="56" t="s">
-        <v>3782</v>
+        <v>3772</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>3786</v>
+        <v>3776</v>
       </c>
       <c r="G75">
         <v>48</v>
@@ -26920,7 +26986,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3750</v>
+        <v>3740</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -26933,10 +26999,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3751</v>
+        <v>3741</v>
       </c>
       <c r="C4" t="s">
-        <v>3793</v>
+        <v>3783</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -26952,10 +27018,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3752</v>
+        <v>3742</v>
       </c>
       <c r="C5" t="s">
-        <v>3765</v>
+        <v>3755</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -26971,10 +27037,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3753</v>
+        <v>3743</v>
       </c>
       <c r="C6" t="s">
-        <v>3766</v>
+        <v>3756</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -26987,10 +27053,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3756</v>
+        <v>3746</v>
       </c>
       <c r="C7" t="s">
-        <v>3767</v>
+        <v>3757</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -27003,7 +27069,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3754</v>
+        <v>3744</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -27020,10 +27086,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3755</v>
+        <v>3745</v>
       </c>
       <c r="C9" t="s">
-        <v>3769</v>
+        <v>3759</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -27036,7 +27102,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3814</v>
+        <v>3804</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
@@ -27051,10 +27117,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3791</v>
+        <v>3781</v>
       </c>
       <c r="C11" t="s">
-        <v>3794</v>
+        <v>3784</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -27068,10 +27134,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3792</v>
+        <v>3782</v>
       </c>
       <c r="C12" t="s">
-        <v>3795</v>
+        <v>3785</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -27085,10 +27151,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3807</v>
+        <v>3797</v>
       </c>
       <c r="C13" t="s">
-        <v>3777</v>
+        <v>3767</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -27099,10 +27165,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3808</v>
+        <v>3798</v>
       </c>
       <c r="C14" t="s">
-        <v>3779</v>
+        <v>3769</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -27113,10 +27179,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3809</v>
+        <v>3799</v>
       </c>
       <c r="C15" t="s">
-        <v>3783</v>
+        <v>3773</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -27127,10 +27193,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3810</v>
+        <v>3800</v>
       </c>
       <c r="C16" t="s">
-        <v>3785</v>
+        <v>3775</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -27141,10 +27207,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="56" t="s">
+        <v>3778</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>3788</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>3798</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -27160,10 +27226,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>3779</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>3789</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>3799</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
@@ -27179,10 +27245,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>3790</v>
+        <v>3780</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>3806</v>
+        <v>3796</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
@@ -27198,10 +27264,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>3796</v>
+        <v>3786</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>3800</v>
+        <v>3790</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -27215,10 +27281,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>3801</v>
+        <v>3791</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>3802</v>
+        <v>3792</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -27232,10 +27298,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>3797</v>
+        <v>3787</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3804</v>
+        <v>3794</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -27249,10 +27315,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>3803</v>
+        <v>3793</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>3805</v>
+        <v>3795</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -27266,7 +27332,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>3811</v>
+        <v>3801</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>464</v>
@@ -27487,10 +27553,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>3733</v>
+        <v>3723</v>
       </c>
       <c r="C3" t="s">
-        <v>3732</v>
+        <v>3722</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -27501,10 +27567,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3710</v>
+        <v>3700</v>
       </c>
       <c r="C4" t="s">
-        <v>3711</v>
+        <v>3701</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -27521,7 +27587,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3712</v>
+        <v>3702</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -27538,10 +27604,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3713</v>
+        <v>3703</v>
       </c>
       <c r="C6" t="s">
-        <v>3717</v>
+        <v>3707</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -27558,7 +27624,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3714</v>
+        <v>3704</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -27575,10 +27641,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3715</v>
+        <v>3705</v>
       </c>
       <c r="C8" t="s">
-        <v>3721</v>
+        <v>3711</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -27595,10 +27661,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3716</v>
+        <v>3706</v>
       </c>
       <c r="C9" t="s">
-        <v>3718</v>
+        <v>3708</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -27615,10 +27681,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>3719</v>
+        <v>3709</v>
       </c>
       <c r="C10" t="s">
-        <v>3724</v>
+        <v>3714</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>22</v>
@@ -27632,10 +27698,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3734</v>
+        <v>3724</v>
       </c>
       <c r="C11" t="s">
-        <v>3736</v>
+        <v>3726</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>22</v>
@@ -27649,10 +27715,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3720</v>
+        <v>3710</v>
       </c>
       <c r="C12" t="s">
-        <v>3725</v>
+        <v>3715</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>22</v>
@@ -27666,10 +27732,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3735</v>
+        <v>3725</v>
       </c>
       <c r="C13" t="s">
-        <v>3737</v>
+        <v>3727</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>22</v>
@@ -27683,10 +27749,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3722</v>
+        <v>3712</v>
       </c>
       <c r="C14" t="s">
-        <v>3726</v>
+        <v>3716</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>22</v>
@@ -27700,10 +27766,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3728</v>
+        <v>3718</v>
       </c>
       <c r="C15" t="s">
-        <v>3730</v>
+        <v>3720</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>22</v>
@@ -27717,10 +27783,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3723</v>
+        <v>3713</v>
       </c>
       <c r="C16" t="s">
-        <v>3727</v>
+        <v>3717</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>22</v>
@@ -27734,10 +27800,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>3729</v>
+        <v>3719</v>
       </c>
       <c r="C17" t="s">
-        <v>3731</v>
+        <v>3721</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>22</v>
@@ -28507,10 +28573,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3602</v>
+        <v>3592</v>
       </c>
       <c r="C2" t="s">
-        <v>3603</v>
+        <v>3593</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -28523,13 +28589,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3610</v>
+        <v>3600</v>
       </c>
       <c r="C3" t="s">
-        <v>3611</v>
+        <v>3601</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="E3" s="4"/>
       <c r="G3">
@@ -28541,10 +28607,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3604</v>
+        <v>3594</v>
       </c>
       <c r="C4" t="s">
-        <v>3605</v>
+        <v>3595</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -28559,16 +28625,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3612</v>
+        <v>3602</v>
       </c>
       <c r="C5" t="s">
-        <v>3613</v>
+        <v>3603</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -28582,16 +28648,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3615</v>
+        <v>3605</v>
       </c>
       <c r="C6" t="s">
-        <v>3616</v>
+        <v>3606</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -28602,10 +28668,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3606</v>
+        <v>3596</v>
       </c>
       <c r="C7" t="s">
-        <v>3607</v>
+        <v>3597</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -28620,16 +28686,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3620</v>
+        <v>3610</v>
       </c>
       <c r="C8" t="s">
-        <v>3617</v>
+        <v>3607</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>3614</v>
+        <v>3604</v>
       </c>
       <c r="G8">
         <v>21</v>
@@ -28640,10 +28706,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>3608</v>
+        <v>3598</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>3609</v>
+        <v>3599</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -28904,10 +28970,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>3621</v>
+        <v>3611</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>3618</v>
+        <v>3608</v>
       </c>
       <c r="G26">
         <v>22</v>
@@ -28918,10 +28984,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>3622</v>
+        <v>3612</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>3619</v>
+        <v>3609</v>
       </c>
       <c r="G27">
         <v>23</v>
@@ -28989,7 +29055,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3636</v>
+        <v>3626</v>
       </c>
       <c r="C3" t="s">
         <v>2070</v>
@@ -29006,10 +29072,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3635</v>
+        <v>3625</v>
       </c>
       <c r="C4" t="s">
-        <v>3634</v>
+        <v>3624</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -29040,7 +29106,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3633</v>
+        <v>3623</v>
       </c>
       <c r="C6" t="s">
         <v>3470</v>
@@ -29057,7 +29123,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3632</v>
+        <v>3622</v>
       </c>
       <c r="C7" t="s">
         <v>2880</v>
@@ -29074,7 +29140,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3631</v>
+        <v>3621</v>
       </c>
       <c r="C8" t="s">
         <v>1082</v>
@@ -29091,7 +29157,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>3630</v>
+        <v>3620</v>
       </c>
       <c r="C9" t="s">
         <v>3481</v>
@@ -29105,7 +29171,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>3629</v>
+        <v>3619</v>
       </c>
       <c r="C10" t="s">
         <v>3482</v>
@@ -29119,7 +29185,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3628</v>
+        <v>3618</v>
       </c>
       <c r="C11" t="s">
         <v>2897</v>
@@ -29133,7 +29199,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>3627</v>
+        <v>3617</v>
       </c>
       <c r="C12" t="s">
         <v>2898</v>
@@ -29147,7 +29213,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>3626</v>
+        <v>3616</v>
       </c>
       <c r="C13" t="s">
         <v>1148</v>
@@ -29161,7 +29227,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>3625</v>
+        <v>3615</v>
       </c>
       <c r="C14" t="s">
         <v>1152</v>
@@ -29175,7 +29241,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>3624</v>
+        <v>3614</v>
       </c>
       <c r="C15" t="s">
         <v>3488</v>
@@ -29189,7 +29255,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>3623</v>
+        <v>3613</v>
       </c>
       <c r="C16" t="s">
         <v>3489</v>
@@ -29431,10 +29497,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3596</v>
+        <v>3586</v>
       </c>
       <c r="C3" t="s">
-        <v>3597</v>
+        <v>3587</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -29449,10 +29515,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>3598</v>
+        <v>3588</v>
       </c>
       <c r="C4" t="s">
-        <v>3599</v>
+        <v>3589</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -29467,10 +29533,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>3600</v>
+        <v>3590</v>
       </c>
       <c r="C5" t="s">
-        <v>3601</v>
+        <v>3591</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -29528,7 +29594,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="4"/>
   </cols>
@@ -29578,7 +29644,7 @@
         <v>3574</v>
       </c>
       <c r="C3" t="s">
-        <v>3591</v>
+        <v>3582</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -29615,7 +29681,7 @@
         <v>3576</v>
       </c>
       <c r="C5" t="s">
-        <v>3587</v>
+        <v>3581</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -29632,7 +29698,7 @@
         <v>3577</v>
       </c>
       <c r="C6" t="s">
-        <v>3588</v>
+        <v>3917</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -29649,7 +29715,7 @@
         <v>3578</v>
       </c>
       <c r="C7" t="s">
-        <v>3589</v>
+        <v>3918</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -29691,10 +29757,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>3581</v>
+        <v>3905</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2945</v>
+        <v>3919</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
@@ -29708,10 +29774,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>3582</v>
+        <v>3906</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>3590</v>
+        <v>3920</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
@@ -29728,10 +29794,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>3583</v>
+        <v>3907</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>3592</v>
+        <v>3921</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
@@ -29745,10 +29811,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>3584</v>
+        <v>3908</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>3593</v>
+        <v>3583</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -29765,10 +29831,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>3585</v>
+        <v>3909</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3594</v>
+        <v>3584</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
@@ -29785,10 +29851,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>3586</v>
+        <v>3910</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3595</v>
+        <v>3585</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
@@ -29825,6 +29891,336 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5528327F-E23E-4092-9DB1-A75A9B2D0F69}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3564</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3569</v>
+      </c>
+      <c r="C3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3565</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3567</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3566</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3568</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>3892</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>3896</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3893</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>3897</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>3574</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>3582</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>3575</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>3898</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>3576</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>3899</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>3917</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>3578</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>3918</v>
+      </c>
+      <c r="F12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>3894</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>3900</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>12</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>3895</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>3901</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>3911</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>3919</v>
+      </c>
+      <c r="F15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>3912</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>3920</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>15</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>3913</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>3921</v>
+      </c>
+      <c r="F17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>16</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>3914</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>3902</v>
+      </c>
+      <c r="F18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="15">
+        <v>17</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>3915</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>3903</v>
+      </c>
+      <c r="F19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>18</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>3916</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>3904</v>
+      </c>
+      <c r="F20">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F20">
+    <sortCondition ref="A1:A20"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3901968F-E5DF-4CBD-ADFB-08FA8A3F4044}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G299"/>
@@ -34110,7 +34506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40963FC-D1AF-47E5-BB09-9770285565C2}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:G27"/>
@@ -34610,7 +35006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEED51C0-16CE-493B-ACDF-CED633B09365}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:G8"/>
@@ -34773,7 +35169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6ED802-F57E-44A6-B120-12D8C7BE7DFE}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G9"/>
@@ -34909,170 +35305,6 @@
       <c r="B9" s="1"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
-  <sheetPr codeName="Sheet25"/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="39.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2946</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2945</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2956</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2947</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>2963</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2962</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>2957</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2564</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="G6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>2958</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2960</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>2959</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2961</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B9" s="6"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="6"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -35997,6 +36229,170 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462C4AB0-4E6A-4C7D-B4F9-5EEC39E547B7}">
+  <sheetPr codeName="Sheet25"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="39.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2947</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2962</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="G8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B9" s="6"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="B10" s="6"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D796DA-5338-470F-A957-675142025379}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:G68"/>
@@ -37353,7 +37749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B1F2EF-0DC6-4BB2-8172-4E4198527108}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:G28"/>
@@ -37844,7 +38240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9AECBD-480E-4512-85A2-339B0B868905}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:G10"/>
@@ -38032,7 +38428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8A30F5-000A-47BE-A26C-2B122315A681}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:G17"/>
@@ -38357,7 +38753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACBD86F-E8B3-46C8-B8DA-0554A39A90B8}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:G10"/>
@@ -38578,7 +38974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78003282-BF12-4B9E-88E0-0647BA982AE8}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:G29"/>
@@ -39056,7 +39452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8BF486-9605-4C14-9D33-B85EFC67F833}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:G11"/>
@@ -39238,7 +39634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF0C918-C1C4-4CA0-AE17-312A0FD1DCCE}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:G51"/>
@@ -40195,7 +40591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC122C9-2D95-4069-BA3C-DDFB1C7F608D}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:G11"/>
@@ -40354,395 +40750,6 @@
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G7">
     <sortCondition ref="A1:A7"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
-  <sheetPr codeName="Sheet31"/>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="58.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2828</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2524</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2755</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2830</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2836</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2831</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2554</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2823</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2832</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2824</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2833</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2825</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2849</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>2826</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2850</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2827</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>2540</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2834</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>2541</v>
-      </c>
-      <c r="C14" t="s">
-        <v>2835</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>2813</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2841</v>
-      </c>
-      <c r="G15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>2814</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2842</v>
-      </c>
-      <c r="G16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>2815</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2843</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>2816</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2844</v>
-      </c>
-      <c r="G18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>2837</v>
-      </c>
-      <c r="C19" t="s">
-        <v>2845</v>
-      </c>
-      <c r="G19">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>2838</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2846</v>
-      </c>
-      <c r="G20">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>2839</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2847</v>
-      </c>
-      <c r="G21">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>2840</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2848</v>
-      </c>
-      <c r="G22">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G22">
-    <sortCondition ref="A1:A22"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40840,7 +40847,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3815</v>
+        <v>3805</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -40857,10 +40864,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3816</v>
+        <v>3806</v>
       </c>
       <c r="C6" t="s">
-        <v>3817</v>
+        <v>3807</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -41354,10 +41361,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3847</v>
+        <v>3837</v>
       </c>
       <c r="C31" t="s">
-        <v>3848</v>
+        <v>3838</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>22</v>
@@ -41497,7 +41504,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3818</v>
+        <v>3808</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>22</v>
@@ -41511,7 +41518,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3819</v>
+        <v>3809</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>22</v>
@@ -41565,10 +41572,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>3849</v>
+        <v>3839</v>
       </c>
       <c r="C42" t="s">
-        <v>3851</v>
+        <v>3841</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>22</v>
@@ -41582,10 +41589,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>3850</v>
+        <v>3840</v>
       </c>
       <c r="C43" t="s">
-        <v>3852</v>
+        <v>3842</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>22</v>
@@ -43432,10 +43439,10 @@
         <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>3853</v>
+        <v>3843</v>
       </c>
       <c r="C128" t="s">
-        <v>3854</v>
+        <v>3844</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>22</v>
@@ -43449,10 +43456,10 @@
         <v>127</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>3855</v>
+        <v>3845</v>
       </c>
       <c r="C129" t="s">
-        <v>3856</v>
+        <v>3846</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>22</v>
@@ -43678,10 +43685,10 @@
         <v>138</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>3824</v>
+        <v>3814</v>
       </c>
       <c r="C140" t="s">
-        <v>3857</v>
+        <v>3847</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>22</v>
@@ -43924,7 +43931,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>3823</v>
+        <v>3813</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>22</v>
@@ -44436,10 +44443,10 @@
         <v>175</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>3825</v>
+        <v>3815</v>
       </c>
       <c r="C177" t="s">
-        <v>3858</v>
+        <v>3848</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>22</v>
@@ -44456,7 +44463,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>3826</v>
+        <v>3816</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>22</v>
@@ -45067,10 +45074,10 @@
         <v>207</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>3821</v>
+        <v>3811</v>
       </c>
       <c r="C209" t="s">
-        <v>3859</v>
+        <v>3849</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>22</v>
@@ -45107,10 +45114,10 @@
         <v>209</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>3820</v>
+        <v>3810</v>
       </c>
       <c r="C211" t="s">
-        <v>3860</v>
+        <v>3850</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>22</v>
@@ -45167,10 +45174,10 @@
         <v>212</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>3827</v>
+        <v>3817</v>
       </c>
       <c r="C214" t="s">
-        <v>3863</v>
+        <v>3853</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>22</v>
@@ -45207,10 +45214,10 @@
         <v>214</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>3828</v>
+        <v>3818</v>
       </c>
       <c r="C216" t="s">
-        <v>3861</v>
+        <v>3851</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>22</v>
@@ -45307,10 +45314,10 @@
         <v>219</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>3829</v>
+        <v>3819</v>
       </c>
       <c r="C221" t="s">
-        <v>3862</v>
+        <v>3852</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>22</v>
@@ -45327,10 +45334,10 @@
         <v>220</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>3822</v>
+        <v>3812</v>
       </c>
       <c r="C222" t="s">
-        <v>3864</v>
+        <v>3854</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>22</v>
@@ -45510,10 +45517,10 @@
         <v>229</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>3865</v>
+        <v>3855</v>
       </c>
       <c r="C231" t="s">
-        <v>3867</v>
+        <v>3857</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>22</v>
@@ -45527,10 +45534,10 @@
         <v>230</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>3866</v>
+        <v>3856</v>
       </c>
       <c r="C232" t="s">
-        <v>3868</v>
+        <v>3858</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>22</v>
@@ -45707,10 +45714,10 @@
         <v>239</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>3830</v>
+        <v>3820</v>
       </c>
       <c r="C241" t="s">
-        <v>3869</v>
+        <v>3859</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>22</v>
@@ -45727,10 +45734,10 @@
         <v>240</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>3831</v>
+        <v>3821</v>
       </c>
       <c r="C242" t="s">
-        <v>3870</v>
+        <v>3860</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>22</v>
@@ -45747,10 +45754,10 @@
         <v>241</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>3832</v>
+        <v>3822</v>
       </c>
       <c r="C243" t="s">
-        <v>3871</v>
+        <v>3861</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>22</v>
@@ -45767,10 +45774,10 @@
         <v>242</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>3833</v>
+        <v>3823</v>
       </c>
       <c r="C244" t="s">
-        <v>3872</v>
+        <v>3862</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>22</v>
@@ -46367,10 +46374,10 @@
         <v>272</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>3834</v>
+        <v>3824</v>
       </c>
       <c r="C274" t="s">
-        <v>3873</v>
+        <v>3863</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>22</v>
@@ -46455,10 +46462,10 @@
         <v>277</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>3742</v>
+        <v>3732</v>
       </c>
       <c r="C279" t="s">
-        <v>3744</v>
+        <v>3734</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>22</v>
@@ -46472,10 +46479,10 @@
         <v>278</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>3743</v>
+        <v>3733</v>
       </c>
       <c r="C280" t="s">
-        <v>3745</v>
+        <v>3735</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>22</v>
@@ -46523,10 +46530,10 @@
         <v>281</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>3738</v>
+        <v>3728</v>
       </c>
       <c r="C283" t="s">
-        <v>3740</v>
+        <v>3730</v>
       </c>
       <c r="E283" s="4" t="s">
         <v>22</v>
@@ -46540,10 +46547,10 @@
         <v>282</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>3739</v>
+        <v>3729</v>
       </c>
       <c r="C284" t="s">
-        <v>3741</v>
+        <v>3731</v>
       </c>
       <c r="E284" s="4" t="s">
         <v>22</v>
@@ -47169,10 +47176,10 @@
         <v>319</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>3835</v>
+        <v>3825</v>
       </c>
       <c r="C321" t="s">
-        <v>3874</v>
+        <v>3864</v>
       </c>
       <c r="E321" s="4" t="s">
         <v>22</v>
@@ -47186,10 +47193,10 @@
         <v>320</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>3836</v>
+        <v>3826</v>
       </c>
       <c r="C322" t="s">
-        <v>3875</v>
+        <v>3865</v>
       </c>
       <c r="E322" s="4" t="s">
         <v>22</v>
@@ -47374,10 +47381,10 @@
         <v>330</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>3837</v>
+        <v>3827</v>
       </c>
       <c r="C332" t="s">
-        <v>3876</v>
+        <v>3866</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>22</v>
@@ -47522,10 +47529,10 @@
         <v>338</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>3838</v>
+        <v>3828</v>
       </c>
       <c r="C340" t="s">
-        <v>3877</v>
+        <v>3867</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>22</v>
@@ -47562,10 +47569,10 @@
         <v>340</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>3839</v>
+        <v>3829</v>
       </c>
       <c r="C342" t="s">
-        <v>3878</v>
+        <v>3868</v>
       </c>
       <c r="G342">
         <v>269</v>
@@ -47841,10 +47848,10 @@
         <v>355</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>3841</v>
+        <v>3831</v>
       </c>
       <c r="C357" t="s">
-        <v>3879</v>
+        <v>3869</v>
       </c>
       <c r="E357" s="4" t="s">
         <v>22</v>
@@ -47858,10 +47865,10 @@
         <v>356</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>3840</v>
+        <v>3830</v>
       </c>
       <c r="C358" t="s">
-        <v>3880</v>
+        <v>3870</v>
       </c>
       <c r="E358" s="4" t="s">
         <v>22</v>
@@ -47875,10 +47882,10 @@
         <v>357</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>3881</v>
+        <v>3871</v>
       </c>
       <c r="C359" t="s">
-        <v>3883</v>
+        <v>3873</v>
       </c>
       <c r="E359" s="4" t="s">
         <v>22</v>
@@ -47892,10 +47899,10 @@
         <v>358</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>3882</v>
+        <v>3872</v>
       </c>
       <c r="C360" t="s">
-        <v>3884</v>
+        <v>3874</v>
       </c>
       <c r="E360" s="4" t="s">
         <v>22</v>
@@ -48045,10 +48052,10 @@
         <v>367</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>3842</v>
+        <v>3832</v>
       </c>
       <c r="C369" t="s">
-        <v>3885</v>
+        <v>3875</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>22</v>
@@ -48065,10 +48072,10 @@
         <v>368</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>3843</v>
+        <v>3833</v>
       </c>
       <c r="C370" t="s">
-        <v>3886</v>
+        <v>3876</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>22</v>
@@ -48085,10 +48092,10 @@
         <v>369</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>3844</v>
+        <v>3834</v>
       </c>
       <c r="C371" t="s">
-        <v>3887</v>
+        <v>3877</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>22</v>
@@ -48105,7 +48112,7 @@
         <v>370</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>3845</v>
+        <v>3835</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>22</v>
@@ -48122,7 +48129,7 @@
         <v>371</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>3846</v>
+        <v>3836</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>22</v>
@@ -48145,6 +48152,395 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52945836-CF67-4AC6-AA8E-A2F75421485D}">
+  <sheetPr codeName="Sheet31"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="58.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2850</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2834</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2835</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2841</v>
+      </c>
+      <c r="G15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2842</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2843</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2844</v>
+      </c>
+      <c r="G18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2845</v>
+      </c>
+      <c r="G19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2846</v>
+      </c>
+      <c r="G20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>2839</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2847</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2848</v>
+      </c>
+      <c r="G22">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G22">
+    <sortCondition ref="A1:A22"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8646CBD5-4903-4B76-AD7B-5FD2C3CD84EA}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:G13"/>
@@ -48392,7 +48788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EAFC06-5BD2-40F9-AAC9-8F399DCA30B2}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:G10"/>
@@ -48533,7 +48929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC071D7-60DD-4BDD-A755-73C9A47CE710}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:G10"/>
@@ -48736,7 +49132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E52B18-32F2-44AB-BEB9-1A4D38FC3321}">
   <sheetPr codeName="Sheet42"/>
   <dimension ref="A1:F29"/>
@@ -48808,10 +49204,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>3627</v>
+      </c>
+      <c r="C4" t="s">
         <v>3637</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3647</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -48826,10 +49222,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>3628</v>
+      </c>
+      <c r="C5" t="s">
         <v>3638</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3648</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -48844,10 +49240,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>3629</v>
+      </c>
+      <c r="C6" t="s">
         <v>3639</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3649</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -48864,10 +49260,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3641</v>
+        <v>3631</v>
       </c>
       <c r="C7" t="s">
-        <v>3650</v>
+        <v>3640</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -48884,10 +49280,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>3634</v>
+      </c>
+      <c r="C8" t="s">
         <v>3644</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3654</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -48904,10 +49300,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>3635</v>
+      </c>
+      <c r="C9" t="s">
         <v>3645</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3655</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -48924,10 +49320,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3640</v>
+        <v>3630</v>
       </c>
       <c r="C10" t="s">
-        <v>3651</v>
+        <v>3641</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
@@ -48944,10 +49340,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>3636</v>
+      </c>
+      <c r="C11" t="s">
         <v>3646</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3656</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
@@ -48964,10 +49360,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>3632</v>
+      </c>
+      <c r="C12" t="s">
         <v>3642</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3652</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
@@ -48984,10 +49380,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>3633</v>
+      </c>
+      <c r="C13" t="s">
         <v>3643</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3653</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -49088,7 +49484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD168143-EF2F-4DA8-9552-0152D380A4CE}">
   <sheetPr codeName="Sheet43"/>
   <dimension ref="A1:F30"/>
@@ -49142,10 +49538,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3705</v>
+        <v>3695</v>
       </c>
       <c r="C3" t="s">
-        <v>3706</v>
+        <v>3696</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -49160,10 +49556,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3657</v>
+        <v>3647</v>
       </c>
       <c r="C4" t="s">
-        <v>3660</v>
+        <v>3650</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -49180,10 +49576,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3658</v>
+        <v>3648</v>
       </c>
       <c r="C5" t="s">
-        <v>3661</v>
+        <v>3651</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -49198,10 +49594,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3659</v>
+        <v>3649</v>
       </c>
       <c r="C6" t="s">
-        <v>3662</v>
+        <v>3652</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -49339,7 +49735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0CB622-4366-4796-A425-D38A6B94B7C7}">
   <sheetPr codeName="Sheet44"/>
   <dimension ref="A1:G29"/>
@@ -49396,10 +49792,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3663</v>
+        <v>3653</v>
       </c>
       <c r="C3" t="s">
-        <v>3664</v>
+        <v>3654</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -49419,10 +49815,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3665</v>
+        <v>3655</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3672</v>
+        <v>3662</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -49437,10 +49833,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3657</v>
+        <v>3647</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3660</v>
+        <v>3650</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -49457,10 +49853,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>3666</v>
+        <v>3656</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>3673</v>
+        <v>3663</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -49475,10 +49871,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>3667</v>
+        <v>3657</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>3674</v>
+        <v>3664</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -49495,10 +49891,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>3668</v>
+        <v>3658</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>3675</v>
+        <v>3665</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -49515,10 +49911,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>3669</v>
+        <v>3659</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>3676</v>
+        <v>3666</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>22</v>
@@ -49535,10 +49931,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>3670</v>
+        <v>3660</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>3677</v>
+        <v>3667</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
@@ -49555,10 +49951,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>3671</v>
+        <v>3661</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>3678</v>
+        <v>3668</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
@@ -49666,7 +50062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B736A4E-0AE1-484F-B09E-E75E07B5469B}">
   <sheetPr codeName="Sheet45"/>
   <dimension ref="A1:F30"/>
@@ -49720,10 +50116,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3679</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="s">
-        <v>3686</v>
+        <v>3676</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -49738,10 +50134,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3689</v>
+        <v>3679</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3690</v>
+        <v>3680</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -49756,10 +50152,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3684</v>
+        <v>3674</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -49774,10 +50170,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3681</v>
+        <v>3671</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3685</v>
+        <v>3675</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -49792,10 +50188,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3682</v>
+        <v>3672</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3687</v>
+        <v>3677</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -49812,10 +50208,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>3683</v>
+        <v>3673</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3688</v>
+        <v>3678</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -49946,7 +50342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5E88C9-7DBC-4DF3-8CB1-5BAAF4537407}">
   <sheetPr codeName="Sheet46"/>
   <dimension ref="A1:G30"/>
@@ -50003,10 +50399,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3691</v>
+        <v>3681</v>
       </c>
       <c r="C3" t="s">
-        <v>3696</v>
+        <v>3686</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -50021,10 +50417,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>3692</v>
+        <v>3682</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>3697</v>
+        <v>3687</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -50039,10 +50435,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>3629</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>3639</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3649</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -50059,10 +50455,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3693</v>
+        <v>3683</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3698</v>
+        <v>3688</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -50082,10 +50478,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>3694</v>
+        <v>3684</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3699</v>
+        <v>3689</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -50105,10 +50501,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>3695</v>
+        <v>3685</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3700</v>
+        <v>3690</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>22</v>
@@ -50239,7 +50635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C075FD25-724E-4851-9475-612792A0E498}">
   <sheetPr codeName="Sheet47"/>
   <dimension ref="A1:F30"/>
@@ -50293,10 +50689,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3691</v>
+        <v>3681</v>
       </c>
       <c r="C3" t="s">
-        <v>3696</v>
+        <v>3686</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -50311,10 +50707,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>3692</v>
+        <v>3682</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>3701</v>
+        <v>3691</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -50329,10 +50725,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3702</v>
+        <v>3692</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3703</v>
+        <v>3693</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>22</v>
@@ -50347,10 +50743,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3707</v>
+        <v>3697</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3704</v>
+        <v>3694</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -50609,7 +51005,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3815</v>
+        <v>3805</v>
       </c>
       <c r="C5" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B5,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -50636,7 +51032,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3816</v>
+        <v>3806</v>
       </c>
       <c r="C6" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B6,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -51311,7 +51707,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3847</v>
+        <v>3837</v>
       </c>
       <c r="C31" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B31,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -51500,7 +51896,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3818</v>
+        <v>3808</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B38,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -51527,7 +51923,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3819</v>
+        <v>3809</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B39,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -51608,7 +52004,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>3849</v>
+        <v>3839</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B42,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -51635,7 +52031,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>3850</v>
+        <v>3840</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B43,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -53930,7 +54326,7 @@
         <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>3853</v>
+        <v>3843</v>
       </c>
       <c r="C128" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B128,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -53957,7 +54353,7 @@
         <v>127</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>3855</v>
+        <v>3845</v>
       </c>
       <c r="C129" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B129,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -54254,7 +54650,7 @@
         <v>138</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>3824</v>
+        <v>3814</v>
       </c>
       <c r="C140" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B140,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -54578,7 +54974,7 @@
         <v>150</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>3823</v>
+        <v>3813</v>
       </c>
       <c r="C152" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B152,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -55253,7 +55649,7 @@
         <v>175</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>3825</v>
+        <v>3815</v>
       </c>
       <c r="C177" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B177,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -55280,7 +55676,7 @@
         <v>176</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>3826</v>
+        <v>3816</v>
       </c>
       <c r="C178" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B178,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56117,7 +56513,7 @@
         <v>207</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>3821</v>
+        <v>3811</v>
       </c>
       <c r="C209" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B209,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56171,7 +56567,7 @@
         <v>209</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>3820</v>
+        <v>3810</v>
       </c>
       <c r="C211" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B211,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56252,7 +56648,7 @@
         <v>212</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>3827</v>
+        <v>3817</v>
       </c>
       <c r="C214" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B214,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56306,7 +56702,7 @@
         <v>214</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>3828</v>
+        <v>3818</v>
       </c>
       <c r="C216" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B216,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56441,7 +56837,7 @@
         <v>219</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>3829</v>
+        <v>3819</v>
       </c>
       <c r="C221" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B221,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56468,7 +56864,7 @@
         <v>220</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>3822</v>
+        <v>3812</v>
       </c>
       <c r="C222" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B222,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56711,7 +57107,7 @@
         <v>229</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>3865</v>
+        <v>3855</v>
       </c>
       <c r="C231" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B231,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56738,7 +57134,7 @@
         <v>230</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>3866</v>
+        <v>3856</v>
       </c>
       <c r="C232" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B232,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -56981,7 +57377,7 @@
         <v>239</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>3830</v>
+        <v>3820</v>
       </c>
       <c r="C241" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B241,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -57008,7 +57404,7 @@
         <v>240</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>3831</v>
+        <v>3821</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B242,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -57035,7 +57431,7 @@
         <v>241</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>3832</v>
+        <v>3822</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B243,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -57062,7 +57458,7 @@
         <v>242</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>3833</v>
+        <v>3823</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B244,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -57872,7 +58268,7 @@
         <v>272</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>3834</v>
+        <v>3824</v>
       </c>
       <c r="C274" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B274,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -58007,7 +58403,7 @@
         <v>277</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>3742</v>
+        <v>3732</v>
       </c>
       <c r="C279" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B279,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -58034,7 +58430,7 @@
         <v>278</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>3743</v>
+        <v>3733</v>
       </c>
       <c r="C280" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B280,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -58115,7 +58511,7 @@
         <v>281</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>3738</v>
+        <v>3728</v>
       </c>
       <c r="C283" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B283,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -58142,7 +58538,7 @@
         <v>282</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>3739</v>
+        <v>3729</v>
       </c>
       <c r="C284" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B284,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -59141,7 +59537,7 @@
         <v>319</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>3835</v>
+        <v>3825</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B321,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -59168,7 +59564,7 @@
         <v>320</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>3836</v>
+        <v>3826</v>
       </c>
       <c r="C322" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B322,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -59438,7 +59834,7 @@
         <v>330</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>3837</v>
+        <v>3827</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B332,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -59654,7 +60050,7 @@
         <v>338</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>3838</v>
+        <v>3828</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B340,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -59708,7 +60104,7 @@
         <v>340</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>3839</v>
+        <v>3829</v>
       </c>
       <c r="C342" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B342,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60113,7 +60509,7 @@
         <v>355</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>3841</v>
+        <v>3831</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B357,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60140,7 +60536,7 @@
         <v>356</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>3840</v>
+        <v>3830</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B358,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60167,7 +60563,7 @@
         <v>357</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>3881</v>
+        <v>3871</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B359,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60194,7 +60590,7 @@
         <v>358</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>3882</v>
+        <v>3872</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B360,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60437,7 +60833,7 @@
         <v>367</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>3842</v>
+        <v>3832</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B369,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60464,7 +60860,7 @@
         <v>368</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>3843</v>
+        <v>3833</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B370,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60491,7 +60887,7 @@
         <v>369</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>3844</v>
+        <v>3834</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B371,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60518,7 +60914,7 @@
         <v>370</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>3845</v>
+        <v>3835</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B372,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -60545,7 +60941,7 @@
         <v>371</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>3846</v>
+        <v>3836</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B373,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -62583,10 +62979,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>3894</v>
+        <v>3884</v>
       </c>
       <c r="C41" t="s">
-        <v>3897</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -62594,10 +62990,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>3895</v>
+        <v>3885</v>
       </c>
       <c r="C42" t="s">
-        <v>3898</v>
+        <v>3888</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -62608,10 +63004,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>3896</v>
+        <v>3886</v>
       </c>
       <c r="C43" t="s">
-        <v>3899</v>
+        <v>3889</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -62622,10 +63018,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>3900</v>
+        <v>3890</v>
       </c>
       <c r="C44" t="s">
-        <v>3901</v>
+        <v>3891</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -70612,7 +71008,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>3888</v>
+        <v>3878</v>
       </c>
       <c r="C4" t="s">
         <v>2065</v>
@@ -70680,7 +71076,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>3889</v>
+        <v>3879</v>
       </c>
       <c r="C8" t="s">
         <v>2054</v>
@@ -70792,7 +71188,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3815</v>
+        <v>3805</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B13,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -70819,7 +71215,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3816</v>
+        <v>3806</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B14,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -71494,7 +71890,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3847</v>
+        <v>3837</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B39,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -71683,7 +72079,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>3818</v>
+        <v>3808</v>
       </c>
       <c r="C46" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B46,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -71710,7 +72106,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>3819</v>
+        <v>3809</v>
       </c>
       <c r="C47" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B47,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -71791,7 +72187,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>3849</v>
+        <v>3839</v>
       </c>
       <c r="C50" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B50,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -71818,7 +72214,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>3850</v>
+        <v>3840</v>
       </c>
       <c r="C51" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B51,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -74113,7 +74509,7 @@
         <v>134</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>3853</v>
+        <v>3843</v>
       </c>
       <c r="C136" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B136,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -74140,7 +74536,7 @@
         <v>135</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>3855</v>
+        <v>3845</v>
       </c>
       <c r="C137" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B137,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -74437,7 +74833,7 @@
         <v>146</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>3824</v>
+        <v>3814</v>
       </c>
       <c r="C148" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B148,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -74761,7 +75157,7 @@
         <v>158</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>3823</v>
+        <v>3813</v>
       </c>
       <c r="C160" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B160,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -75436,7 +75832,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>3825</v>
+        <v>3815</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B185,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -75463,7 +75859,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>3826</v>
+        <v>3816</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B186,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76300,7 +76696,7 @@
         <v>215</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>3821</v>
+        <v>3811</v>
       </c>
       <c r="C217" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B217,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76354,7 +76750,7 @@
         <v>217</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>3820</v>
+        <v>3810</v>
       </c>
       <c r="C219" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B219,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76435,7 +76831,7 @@
         <v>220</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>3827</v>
+        <v>3817</v>
       </c>
       <c r="C222" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B222,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76489,7 +76885,7 @@
         <v>222</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>3828</v>
+        <v>3818</v>
       </c>
       <c r="C224" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B224,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76624,7 +77020,7 @@
         <v>227</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>3829</v>
+        <v>3819</v>
       </c>
       <c r="C229" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B229,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76651,7 +77047,7 @@
         <v>228</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>3822</v>
+        <v>3812</v>
       </c>
       <c r="C230" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B230,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76894,7 +77290,7 @@
         <v>237</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>3865</v>
+        <v>3855</v>
       </c>
       <c r="C239" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B239,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -76921,7 +77317,7 @@
         <v>238</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>3866</v>
+        <v>3856</v>
       </c>
       <c r="C240" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B240,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -77164,7 +77560,7 @@
         <v>247</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>3830</v>
+        <v>3820</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B249,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -77191,7 +77587,7 @@
         <v>248</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>3831</v>
+        <v>3821</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B250,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -77218,7 +77614,7 @@
         <v>249</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>3832</v>
+        <v>3822</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B251,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -77245,7 +77641,7 @@
         <v>250</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>3833</v>
+        <v>3823</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B252,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -78055,7 +78451,7 @@
         <v>280</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>3834</v>
+        <v>3824</v>
       </c>
       <c r="C282" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B282,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -78190,7 +78586,7 @@
         <v>285</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>3742</v>
+        <v>3732</v>
       </c>
       <c r="C287" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B287,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -78217,7 +78613,7 @@
         <v>286</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>3743</v>
+        <v>3733</v>
       </c>
       <c r="C288" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B288,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -78298,7 +78694,7 @@
         <v>289</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>3738</v>
+        <v>3728</v>
       </c>
       <c r="C291" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B291,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -78325,7 +78721,7 @@
         <v>290</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>3739</v>
+        <v>3729</v>
       </c>
       <c r="C292" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B292,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -79324,7 +79720,7 @@
         <v>327</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>3835</v>
+        <v>3825</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B329,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -79351,7 +79747,7 @@
         <v>328</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>3836</v>
+        <v>3826</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B330,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -79621,7 +80017,7 @@
         <v>338</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>3837</v>
+        <v>3827</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B340,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -79837,7 +80233,7 @@
         <v>346</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>3838</v>
+        <v>3828</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B348,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -79891,7 +80287,7 @@
         <v>348</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>3839</v>
+        <v>3829</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B350,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80296,7 +80692,7 @@
         <v>363</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>3841</v>
+        <v>3831</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B365,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80323,7 +80719,7 @@
         <v>364</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>3840</v>
+        <v>3830</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B366,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80350,7 +80746,7 @@
         <v>365</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>3881</v>
+        <v>3871</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B367,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80377,7 +80773,7 @@
         <v>366</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>3882</v>
+        <v>3872</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B368,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80620,7 +81016,7 @@
         <v>375</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>3842</v>
+        <v>3832</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B377,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80647,7 +81043,7 @@
         <v>376</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>3843</v>
+        <v>3833</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B378,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80674,7 +81070,7 @@
         <v>377</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>3844</v>
+        <v>3834</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B379,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80701,7 +81097,7 @@
         <v>378</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>3845</v>
+        <v>3835</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B380,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
@@ -80728,7 +81124,7 @@
         <v>379</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>3846</v>
+        <v>3836</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.LET(_xlpm.x,VLOOKUP($B381,spell_header!$B$2:$G$373,2,FALSE),IF(_xlpm.x="","",_xlpm.x))</f>
